--- a/output7/【河洛文讀注音-閩拼調號】《桃花源記》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調號】《桃花源記》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4504BDD4-FDEA-4B79-BDDD-ACEED6E84CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A92F070-540A-4910-9C6E-45C84F6C2A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-75" windowWidth="25815" windowHeight="15585" tabRatio="718" activeTab="1" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" tabRatio="718" activeTab="1" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -3637,7 +3637,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3808,29 +3808,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="2" borderId="3" xfId="5" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -4501,49 +4478,49 @@
     <row r="3" spans="1:22" s="12" customFormat="1" ht="60" customHeight="1">
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
-      <c r="D3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q3" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R3" s="58" t="s">
+      <c r="D3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q3" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R3" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S3" s="12" t="s">
@@ -4556,49 +4533,49 @@
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B4" s="14"/>
-      <c r="D4" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="E4" s="59" t="s">
+      <c r="D4" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="E4" s="43" t="s">
         <v>627</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="43" t="s">
         <v>629</v>
       </c>
-      <c r="G4" s="59" t="s">
+      <c r="G4" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="H4" s="59" t="s">
+      <c r="H4" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="I4" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="J4" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="K4" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="L4" s="59" t="s">
+      <c r="I4" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="J4" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="K4" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="L4" s="43" t="s">
         <v>630</v>
       </c>
-      <c r="M4" s="59" t="s">
+      <c r="M4" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="N4" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="O4" s="59" t="s">
+      <c r="N4" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="O4" s="43" t="s">
         <v>399</v>
       </c>
-      <c r="P4" s="59" t="s">
+      <c r="P4" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="Q4" s="59" t="s">
+      <c r="Q4" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="R4" s="59" t="s">
+      <c r="R4" s="43" t="s">
         <v>156</v>
       </c>
       <c r="S4" s="46" t="s">
@@ -4610,49 +4587,49 @@
       <c r="B5" s="15">
         <v>1</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="E5" s="57" t="s">
+      <c r="E5" s="51" t="s">
         <v>409</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="F5" s="51" t="s">
         <v>411</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="G5" s="51" t="s">
         <v>413</v>
       </c>
-      <c r="H5" s="57" t="s">
+      <c r="H5" s="51" t="s">
         <v>414</v>
       </c>
-      <c r="I5" s="57" t="s">
+      <c r="I5" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="K5" s="57" t="s">
+      <c r="K5" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="L5" s="57" t="s">
+      <c r="L5" s="51" t="s">
         <v>415</v>
       </c>
-      <c r="M5" s="57" t="s">
+      <c r="M5" s="51" t="s">
         <v>416</v>
       </c>
-      <c r="N5" s="57" t="s">
+      <c r="N5" s="51" t="s">
         <v>417</v>
       </c>
-      <c r="O5" s="57" t="s">
+      <c r="O5" s="51" t="s">
         <v>419</v>
       </c>
-      <c r="P5" s="57" t="s">
+      <c r="P5" s="51" t="s">
         <v>421</v>
       </c>
-      <c r="Q5" s="57" t="s">
+      <c r="Q5" s="51" t="s">
         <v>261</v>
       </c>
-      <c r="R5" s="57" t="str">
+      <c r="R5" s="51" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -4665,49 +4642,49 @@
     <row r="6" spans="1:22" s="18" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="16"/>
       <c r="C6" s="17"/>
-      <c r="D6" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="59" t="s">
+      <c r="D6" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="43" t="s">
         <v>335</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="43" t="s">
         <v>629</v>
       </c>
-      <c r="G6" s="59" t="s">
+      <c r="G6" s="43" t="s">
         <v>341</v>
       </c>
-      <c r="H6" s="59" t="s">
+      <c r="H6" s="43" t="s">
         <v>392</v>
       </c>
-      <c r="I6" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="J6" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="K6" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="L6" s="59" t="s">
+      <c r="I6" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="J6" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="K6" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="L6" s="43" t="s">
         <v>631</v>
       </c>
-      <c r="M6" s="59" t="s">
+      <c r="M6" s="43" t="s">
         <v>632</v>
       </c>
-      <c r="N6" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="O6" s="59" t="s">
+      <c r="N6" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="O6" s="43" t="s">
         <v>400</v>
       </c>
-      <c r="P6" s="59" t="s">
+      <c r="P6" s="43" t="s">
         <v>326</v>
       </c>
-      <c r="Q6" s="60" t="s">
+      <c r="Q6" s="44" t="s">
         <v>378</v>
       </c>
-      <c r="R6" s="60" t="s">
+      <c r="R6" s="44" t="s">
         <v>156</v>
       </c>
       <c r="S6" s="47" t="s">
@@ -4718,49 +4695,49 @@
     <row r="7" spans="1:22" s="22" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="19"/>
       <c r="C7" s="20"/>
-      <c r="D7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q7" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R7" s="58" t="s">
+      <c r="D7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q7" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R7" s="41" t="s">
         <v>836</v>
       </c>
       <c r="S7" s="48" t="s">
@@ -4770,52 +4747,52 @@
     </row>
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="14"/>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="59" t="s">
+      <c r="E8" s="43" t="s">
         <v>633</v>
       </c>
-      <c r="F8" s="59" t="s">
+      <c r="F8" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="G8" s="59" t="s">
+      <c r="G8" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="H8" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I8" s="59" t="s">
+      <c r="H8" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I8" s="43" t="s">
         <v>315</v>
       </c>
-      <c r="J8" s="59" t="s">
+      <c r="J8" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="K8" s="59" t="s">
+      <c r="K8" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="59" t="s">
+      <c r="L8" s="43" t="s">
         <v>635</v>
       </c>
-      <c r="M8" s="59" t="s">
+      <c r="M8" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="N8" s="59" t="s">
+      <c r="N8" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="O8" s="59" t="s">
+      <c r="O8" s="43" t="s">
         <v>362</v>
       </c>
-      <c r="P8" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q8" s="59" t="s">
+      <c r="P8" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q8" s="43" t="s">
         <v>394</v>
       </c>
-      <c r="R8" s="59" t="s">
+      <c r="R8" s="43" t="s">
         <v>836</v>
       </c>
-      <c r="S8" s="62" t="s">
+      <c r="S8" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V8" s="55"/>
@@ -4825,52 +4802,52 @@
         <f>B5+1</f>
         <v>2</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="51" t="s">
         <v>416</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="51" t="s">
         <v>422</v>
       </c>
-      <c r="F9" s="57" t="s">
+      <c r="F9" s="51" t="s">
         <v>424</v>
       </c>
-      <c r="G9" s="57" t="s">
+      <c r="G9" s="51" t="s">
         <v>253</v>
       </c>
-      <c r="H9" s="57" t="s">
+      <c r="H9" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="51" t="s">
         <v>230</v>
       </c>
-      <c r="J9" s="57" t="s">
+      <c r="J9" s="51" t="s">
         <v>426</v>
       </c>
-      <c r="K9" s="57" t="s">
+      <c r="K9" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="L9" s="57" t="s">
+      <c r="L9" s="51" t="s">
         <v>428</v>
       </c>
-      <c r="M9" s="57" t="s">
+      <c r="M9" s="51" t="s">
         <v>430</v>
       </c>
-      <c r="N9" s="57" t="s">
+      <c r="N9" s="51" t="s">
         <v>431</v>
       </c>
-      <c r="O9" s="57" t="s">
+      <c r="O9" s="51" t="s">
         <v>433</v>
       </c>
-      <c r="P9" s="57" t="s">
+      <c r="P9" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="Q9" s="57" t="s">
+      <c r="Q9" s="51" t="s">
         <v>435</v>
       </c>
-      <c r="R9" s="57" t="s">
+      <c r="R9" s="51" t="s">
         <v>437</v>
       </c>
-      <c r="S9" s="61" t="s">
+      <c r="S9" s="45" t="s">
         <v>156</v>
       </c>
       <c r="T9" s="13"/>
@@ -4878,52 +4855,52 @@
     </row>
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="16"/>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="43" t="s">
         <v>632</v>
       </c>
-      <c r="E10" s="59" t="s">
+      <c r="E10" s="43" t="s">
         <v>294</v>
       </c>
-      <c r="F10" s="59" t="s">
+      <c r="F10" s="43" t="s">
         <v>341</v>
       </c>
-      <c r="G10" s="59" t="s">
+      <c r="G10" s="43" t="s">
         <v>366</v>
       </c>
-      <c r="H10" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I10" s="59" t="s">
+      <c r="H10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I10" s="43" t="s">
         <v>316</v>
       </c>
-      <c r="J10" s="59" t="s">
+      <c r="J10" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="K10" s="59" t="s">
+      <c r="K10" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="L10" s="59" t="s">
+      <c r="L10" s="43" t="s">
         <v>636</v>
       </c>
-      <c r="M10" s="59" t="s">
+      <c r="M10" s="43" t="s">
         <v>286</v>
       </c>
-      <c r="N10" s="59" t="s">
+      <c r="N10" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="O10" s="59" t="s">
+      <c r="O10" s="43" t="s">
         <v>363</v>
       </c>
-      <c r="P10" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q10" s="60" t="s">
+      <c r="P10" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q10" s="44" t="s">
         <v>395</v>
       </c>
-      <c r="R10" s="60" t="s">
+      <c r="R10" s="44" t="s">
         <v>690</v>
       </c>
-      <c r="S10" s="63" t="s">
+      <c r="S10" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V10" s="55"/>
@@ -4931,49 +4908,49 @@
     <row r="11" spans="1:22" s="21" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="23"/>
       <c r="C11" s="24"/>
-      <c r="D11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q11" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R11" s="58" t="s">
+      <c r="D11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q11" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R11" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S11" s="48" t="s">
@@ -4983,52 +4960,52 @@
     </row>
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="14"/>
-      <c r="D12" s="59" t="s">
+      <c r="D12" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="F12" s="59" t="s">
+      <c r="E12" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="G12" s="59" t="s">
+      <c r="G12" s="43" t="s">
         <v>213</v>
       </c>
-      <c r="H12" s="59" t="s">
+      <c r="H12" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="59" t="s">
+      <c r="I12" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="59" t="s">
+      <c r="J12" s="43" t="s">
         <v>637</v>
       </c>
-      <c r="K12" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="L12" s="59" t="s">
+      <c r="K12" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="L12" s="43" t="s">
         <v>389</v>
       </c>
-      <c r="M12" s="59" t="s">
+      <c r="M12" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="N12" s="59" t="s">
+      <c r="N12" s="43" t="s">
         <v>627</v>
       </c>
-      <c r="O12" s="59" t="s">
+      <c r="O12" s="43" t="s">
         <v>629</v>
       </c>
-      <c r="P12" s="59" t="s">
+      <c r="P12" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="Q12" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="R12" s="59" t="s">
+      <c r="Q12" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="R12" s="43" t="s">
         <v>640</v>
       </c>
-      <c r="S12" s="62" t="s">
+      <c r="S12" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V12" s="55"/>
@@ -5038,104 +5015,104 @@
         <f>B9+1</f>
         <v>3</v>
       </c>
-      <c r="D13" s="57" t="s">
+      <c r="D13" s="51" t="s">
         <v>439</v>
       </c>
-      <c r="E13" s="57" t="s">
+      <c r="E13" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="F13" s="57" t="s">
+      <c r="F13" s="51" t="s">
         <v>440</v>
       </c>
-      <c r="G13" s="57" t="s">
+      <c r="G13" s="51" t="s">
         <v>233</v>
       </c>
-      <c r="H13" s="57" t="s">
+      <c r="H13" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="I13" s="57" t="s">
+      <c r="I13" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="J13" s="57" t="s">
+      <c r="J13" s="51" t="s">
         <v>441</v>
       </c>
-      <c r="K13" s="57" t="s">
+      <c r="K13" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="L13" s="57" t="s">
+      <c r="L13" s="51" t="s">
         <v>442</v>
       </c>
-      <c r="M13" s="57" t="s">
+      <c r="M13" s="51" t="s">
         <v>228</v>
       </c>
-      <c r="N13" s="57" t="s">
+      <c r="N13" s="51" t="s">
         <v>409</v>
       </c>
-      <c r="O13" s="57" t="s">
+      <c r="O13" s="51" t="s">
         <v>411</v>
       </c>
-      <c r="P13" s="57" t="s">
+      <c r="P13" s="51" t="s">
         <v>444</v>
       </c>
-      <c r="Q13" s="57" t="s">
+      <c r="Q13" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="R13" s="57" t="s">
+      <c r="R13" s="51" t="s">
         <v>446</v>
       </c>
-      <c r="S13" s="61" t="s">
+      <c r="S13" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V13" s="55"/>
     </row>
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="16"/>
-      <c r="D14" s="59" t="s">
+      <c r="D14" s="43" t="s">
         <v>206</v>
       </c>
-      <c r="E14" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="F14" s="59" t="s">
+      <c r="E14" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" s="43" t="s">
         <v>305</v>
       </c>
-      <c r="G14" s="59" t="s">
+      <c r="G14" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="H14" s="59" t="s">
+      <c r="H14" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="59" t="s">
+      <c r="I14" s="43" t="s">
         <v>373</v>
       </c>
-      <c r="J14" s="59" t="s">
+      <c r="J14" s="43" t="s">
         <v>638</v>
       </c>
-      <c r="K14" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="L14" s="59" t="s">
+      <c r="K14" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="L14" s="43" t="s">
         <v>390</v>
       </c>
-      <c r="M14" s="59" t="s">
+      <c r="M14" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="N14" s="59" t="s">
+      <c r="N14" s="43" t="s">
         <v>335</v>
       </c>
-      <c r="O14" s="59" t="s">
+      <c r="O14" s="43" t="s">
         <v>629</v>
       </c>
-      <c r="P14" s="59" t="s">
+      <c r="P14" s="43" t="s">
         <v>306</v>
       </c>
-      <c r="Q14" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="R14" s="60" t="s">
+      <c r="Q14" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="R14" s="44" t="s">
         <v>641</v>
       </c>
-      <c r="S14" s="63" t="s">
+      <c r="S14" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V14" s="55"/>
@@ -5143,49 +5120,49 @@
     <row r="15" spans="1:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="10"/>
       <c r="C15" s="25"/>
-      <c r="D15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q15" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R15" s="58" t="s">
+      <c r="D15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R15" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S15" s="50" t="s">
@@ -5195,52 +5172,52 @@
     </row>
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="14"/>
-      <c r="D16" s="59" t="s">
+      <c r="D16" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="G16" s="59" t="s">
+      <c r="G16" s="43" t="s">
         <v>635</v>
       </c>
-      <c r="H16" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I16" s="59" t="s">
+      <c r="H16" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I16" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="J16" s="59" t="s">
+      <c r="J16" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="59" t="s">
+      <c r="K16" s="43" t="s">
         <v>643</v>
       </c>
-      <c r="L16" s="59" t="s">
+      <c r="L16" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="M16" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N16" s="59" t="s">
+      <c r="M16" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N16" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="O16" s="59" t="s">
+      <c r="O16" s="43" t="s">
         <v>644</v>
       </c>
-      <c r="P16" s="59" t="s">
+      <c r="P16" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="Q16" s="59" t="s">
+      <c r="Q16" s="43" t="s">
         <v>303</v>
       </c>
-      <c r="R16" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="S16" s="62" t="s">
+      <c r="R16" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="S16" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V16" s="55"/>
@@ -5250,104 +5227,104 @@
         <f>B13+1</f>
         <v>4</v>
       </c>
-      <c r="D17" s="57" t="s">
+      <c r="D17" s="51" t="s">
         <v>448</v>
       </c>
-      <c r="E17" s="57" t="s">
+      <c r="E17" s="51" t="s">
         <v>256</v>
       </c>
-      <c r="F17" s="57" t="s">
+      <c r="F17" s="51" t="s">
         <v>270</v>
       </c>
-      <c r="G17" s="57" t="s">
+      <c r="G17" s="51" t="s">
         <v>450</v>
       </c>
-      <c r="H17" s="57" t="s">
+      <c r="H17" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="I17" s="57" t="s">
+      <c r="I17" s="51" t="s">
         <v>253</v>
       </c>
-      <c r="J17" s="57" t="s">
+      <c r="J17" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="K17" s="57" t="s">
+      <c r="K17" s="51" t="s">
         <v>452</v>
       </c>
-      <c r="L17" s="57" t="s">
+      <c r="L17" s="51" t="s">
         <v>271</v>
       </c>
-      <c r="M17" s="57" t="s">
+      <c r="M17" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="N17" s="57" t="s">
+      <c r="N17" s="51" t="s">
         <v>272</v>
       </c>
-      <c r="O17" s="57" t="s">
+      <c r="O17" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="P17" s="57" t="s">
+      <c r="P17" s="51" t="s">
         <v>454</v>
       </c>
-      <c r="Q17" s="57" t="s">
+      <c r="Q17" s="51" t="s">
         <v>225</v>
       </c>
-      <c r="R17" s="57" t="s">
+      <c r="R17" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="S17" s="61" t="s">
+      <c r="S17" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V17" s="55"/>
     </row>
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="16"/>
-      <c r="D18" s="59" t="s">
+      <c r="D18" s="43" t="s">
         <v>358</v>
       </c>
-      <c r="E18" s="59" t="s">
+      <c r="E18" s="43" t="s">
         <v>201</v>
       </c>
-      <c r="F18" s="59" t="s">
+      <c r="F18" s="43" t="s">
         <v>391</v>
       </c>
-      <c r="G18" s="59" t="s">
+      <c r="G18" s="43" t="s">
         <v>636</v>
       </c>
-      <c r="H18" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I18" s="59" t="s">
+      <c r="H18" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I18" s="43" t="s">
         <v>366</v>
       </c>
-      <c r="J18" s="59" t="s">
+      <c r="J18" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="K18" s="59" t="s">
+      <c r="K18" s="43" t="s">
         <v>643</v>
       </c>
-      <c r="L18" s="59" t="s">
+      <c r="L18" s="43" t="s">
         <v>312</v>
       </c>
-      <c r="M18" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N18" s="59" t="s">
+      <c r="M18" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N18" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="O18" s="59" t="s">
+      <c r="O18" s="43" t="s">
         <v>645</v>
       </c>
-      <c r="P18" s="59" t="s">
+      <c r="P18" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="Q18" s="60" t="s">
+      <c r="Q18" s="44" t="s">
         <v>304</v>
       </c>
-      <c r="R18" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="S18" s="63" t="s">
+      <c r="R18" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="S18" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V18" s="55"/>
@@ -5355,49 +5332,49 @@
     <row r="19" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="10"/>
       <c r="C19" s="25"/>
-      <c r="D19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q19" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R19" s="58" t="s">
+      <c r="D19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q19" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R19" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S19" s="50" t="s">
@@ -5407,52 +5384,52 @@
     </row>
     <row r="20" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="14"/>
-      <c r="D20" s="59" t="s">
+      <c r="D20" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="E20" s="59" t="s">
+      <c r="E20" s="43" t="s">
         <v>384</v>
       </c>
-      <c r="F20" s="59" t="s">
+      <c r="F20" s="43" t="s">
         <v>299</v>
       </c>
-      <c r="G20" s="59" t="s">
+      <c r="G20" s="43" t="s">
         <v>281</v>
       </c>
-      <c r="H20" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I20" s="59" t="s">
+      <c r="H20" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I20" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="J20" s="59" t="s">
+      <c r="J20" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="K20" s="59" t="s">
+      <c r="K20" s="43" t="s">
         <v>647</v>
       </c>
-      <c r="L20" s="59" t="s">
+      <c r="L20" s="43" t="s">
         <v>650</v>
       </c>
-      <c r="M20" s="59" t="s">
+      <c r="M20" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="N20" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="O20" s="59" t="s">
+      <c r="N20" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="O20" s="43" t="s">
         <v>652</v>
       </c>
-      <c r="P20" s="59" t="s">
+      <c r="P20" s="43" t="s">
         <v>653</v>
       </c>
-      <c r="Q20" s="59" t="s">
+      <c r="Q20" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="R20" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="S20" s="62" t="s">
+      <c r="R20" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="S20" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V20" s="55"/>
@@ -5462,104 +5439,104 @@
         <f>B17+1</f>
         <v>5</v>
       </c>
-      <c r="D21" s="57" t="s">
+      <c r="D21" s="51" t="s">
         <v>247</v>
       </c>
-      <c r="E21" s="57" t="s">
+      <c r="E21" s="51" t="s">
         <v>456</v>
       </c>
-      <c r="F21" s="57" t="s">
+      <c r="F21" s="51" t="s">
         <v>458</v>
       </c>
-      <c r="G21" s="57" t="s">
+      <c r="G21" s="51" t="s">
         <v>460</v>
       </c>
-      <c r="H21" s="57" t="s">
+      <c r="H21" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="I21" s="57" t="s">
+      <c r="I21" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="J21" s="57" t="s">
+      <c r="J21" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="K21" s="57" t="s">
+      <c r="K21" s="51" t="s">
         <v>462</v>
       </c>
-      <c r="L21" s="57" t="s">
+      <c r="L21" s="51" t="s">
         <v>464</v>
       </c>
-      <c r="M21" s="57" t="s">
+      <c r="M21" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="N21" s="57" t="s">
+      <c r="N21" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="O21" s="57" t="s">
+      <c r="O21" s="51" t="s">
         <v>465</v>
       </c>
-      <c r="P21" s="57" t="s">
+      <c r="P21" s="51" t="s">
         <v>466</v>
       </c>
-      <c r="Q21" s="57" t="s">
+      <c r="Q21" s="51" t="s">
         <v>439</v>
       </c>
-      <c r="R21" s="57" t="s">
+      <c r="R21" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="S21" s="61" t="s">
+      <c r="S21" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V21" s="55"/>
     </row>
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="16"/>
-      <c r="D22" s="59" t="s">
+      <c r="D22" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="43" t="s">
         <v>385</v>
       </c>
-      <c r="F22" s="59" t="s">
+      <c r="F22" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="G22" s="59" t="s">
+      <c r="G22" s="43" t="s">
         <v>281</v>
       </c>
-      <c r="H22" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I22" s="59" t="s">
+      <c r="H22" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I22" s="43" t="s">
         <v>286</v>
       </c>
-      <c r="J22" s="59" t="s">
+      <c r="J22" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="K22" s="59" t="s">
+      <c r="K22" s="43" t="s">
         <v>648</v>
       </c>
-      <c r="L22" s="59" t="s">
+      <c r="L22" s="43" t="s">
         <v>651</v>
       </c>
-      <c r="M22" s="59" t="s">
+      <c r="M22" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="N22" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="O22" s="59" t="s">
+      <c r="N22" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="O22" s="43" t="s">
         <v>652</v>
       </c>
-      <c r="P22" s="59" t="s">
+      <c r="P22" s="43" t="s">
         <v>654</v>
       </c>
-      <c r="Q22" s="60" t="s">
+      <c r="Q22" s="44" t="s">
         <v>206</v>
       </c>
-      <c r="R22" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="S22" s="63" t="s">
+      <c r="R22" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="S22" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V22" s="55"/>
@@ -5567,22 +5544,22 @@
     <row r="23" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="10"/>
       <c r="C23" s="25"/>
-      <c r="D23" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E23" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F23" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G23" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H23" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I23" s="58" t="s">
+      <c r="D23" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F23" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G23" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H23" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I23" s="41" t="s">
         <v>156</v>
       </c>
       <c r="J23" s="41" t="s">
@@ -5619,22 +5596,22 @@
     </row>
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="14"/>
-      <c r="D24" s="59" t="s">
+      <c r="D24" s="43" t="s">
         <v>655</v>
       </c>
-      <c r="E24" s="59" t="s">
+      <c r="E24" s="43" t="s">
         <v>333</v>
       </c>
-      <c r="F24" s="59" t="s">
+      <c r="F24" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="G24" s="59" t="s">
+      <c r="G24" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="H24" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I24" s="59" t="s">
+      <c r="H24" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I24" s="43" t="s">
         <v>156</v>
       </c>
       <c r="J24" s="43" t="s">
@@ -5674,22 +5651,22 @@
         <f>B21+1</f>
         <v>6</v>
       </c>
-      <c r="D25" s="57" t="s">
+      <c r="D25" s="51" t="s">
         <v>467</v>
       </c>
-      <c r="E25" s="57" t="s">
+      <c r="E25" s="51" t="s">
         <v>240</v>
       </c>
-      <c r="F25" s="57" t="s">
+      <c r="F25" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="G25" s="57" t="s">
+      <c r="G25" s="51" t="s">
         <v>444</v>
       </c>
-      <c r="H25" s="57" t="s">
+      <c r="H25" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="I25" s="57" t="str">
+      <c r="I25" s="51" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -5728,22 +5705,22 @@
     </row>
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="16"/>
-      <c r="D26" s="59" t="s">
+      <c r="D26" s="43" t="s">
         <v>656</v>
       </c>
-      <c r="E26" s="59" t="s">
+      <c r="E26" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="F26" s="59" t="s">
+      <c r="F26" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="G26" s="59" t="s">
+      <c r="G26" s="43" t="s">
         <v>306</v>
       </c>
-      <c r="H26" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I26" s="59" t="s">
+      <c r="H26" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I26" s="43" t="s">
         <v>156</v>
       </c>
       <c r="J26" s="43" t="s">
@@ -5781,49 +5758,49 @@
     <row r="27" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B27" s="10"/>
       <c r="C27" s="25"/>
-      <c r="D27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q27" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R27" s="58" t="s">
+      <c r="D27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q27" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R27" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S27" s="50" t="s">
@@ -5837,52 +5814,52 @@
     </row>
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="14"/>
-      <c r="D28" s="59" t="s">
+      <c r="D28" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="E28" s="59" t="s">
+      <c r="E28" s="43" t="s">
         <v>301</v>
       </c>
-      <c r="F28" s="59" t="s">
+      <c r="F28" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="G28" s="59" t="s">
+      <c r="G28" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="H28" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I28" s="59" t="s">
+      <c r="H28" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I28" s="43" t="s">
         <v>658</v>
       </c>
-      <c r="J28" s="59" t="s">
+      <c r="J28" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="K28" s="59" t="s">
+      <c r="K28" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="L28" s="59" t="s">
+      <c r="L28" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="M28" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N28" s="59" t="s">
+      <c r="M28" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N28" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="O28" s="59" t="s">
+      <c r="O28" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="P28" s="59" t="s">
+      <c r="P28" s="43" t="s">
         <v>660</v>
       </c>
-      <c r="Q28" s="59" t="s">
+      <c r="Q28" s="43" t="s">
         <v>839</v>
       </c>
-      <c r="R28" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="S28" s="62" t="s">
+      <c r="R28" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="S28" s="46" t="s">
         <v>156</v>
       </c>
       <c r="U28" s="26" t="str">
@@ -5896,52 +5873,52 @@
         <f>B25+1</f>
         <v>7</v>
       </c>
-      <c r="D29" s="57" t="s">
+      <c r="D29" s="51" t="s">
         <v>444</v>
       </c>
-      <c r="E29" s="57" t="s">
+      <c r="E29" s="51" t="s">
         <v>224</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="G29" s="57" t="s">
+      <c r="G29" s="51" t="s">
         <v>413</v>
       </c>
-      <c r="H29" s="57" t="s">
+      <c r="H29" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="I29" s="57" t="s">
+      <c r="I29" s="51" t="s">
         <v>469</v>
       </c>
-      <c r="J29" s="57" t="s">
+      <c r="J29" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="K29" s="57" t="s">
+      <c r="K29" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="L29" s="57" t="s">
+      <c r="L29" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="M29" s="57" t="s">
+      <c r="M29" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="N29" s="57" t="s">
+      <c r="N29" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="O29" s="57" t="s">
+      <c r="O29" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="P29" s="57" t="s">
+      <c r="P29" s="51" t="s">
         <v>470</v>
       </c>
-      <c r="Q29" s="57" t="s">
+      <c r="Q29" s="51" t="s">
         <v>471</v>
       </c>
-      <c r="R29" s="57" t="s">
+      <c r="R29" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="S29" s="61" t="s">
+      <c r="S29" s="45" t="s">
         <v>156</v>
       </c>
       <c r="U29" s="26" t="str">
@@ -5952,52 +5929,52 @@
     </row>
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="16"/>
-      <c r="D30" s="59" t="s">
+      <c r="D30" s="43" t="s">
         <v>306</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="43" t="s">
         <v>302</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="G30" s="59" t="s">
+      <c r="G30" s="43" t="s">
         <v>341</v>
       </c>
-      <c r="H30" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I30" s="59" t="s">
+      <c r="H30" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I30" s="43" t="s">
         <v>659</v>
       </c>
-      <c r="J30" s="59" t="s">
+      <c r="J30" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="K30" s="59" t="s">
+      <c r="K30" s="43" t="s">
         <v>354</v>
       </c>
-      <c r="L30" s="59" t="s">
+      <c r="L30" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="M30" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N30" s="59" t="s">
+      <c r="M30" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N30" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="O30" s="59" t="s">
+      <c r="O30" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="P30" s="59" t="s">
+      <c r="P30" s="43" t="s">
         <v>661</v>
       </c>
-      <c r="Q30" s="60" t="s">
+      <c r="Q30" s="44" t="s">
         <v>278</v>
       </c>
-      <c r="R30" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="S30" s="63" t="s">
+      <c r="R30" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="S30" s="49" t="s">
         <v>156</v>
       </c>
       <c r="U30" s="26" t="str">
@@ -6009,49 +5986,49 @@
     <row r="31" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B31" s="10"/>
       <c r="C31" s="25"/>
-      <c r="D31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q31" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R31" s="58" t="s">
+      <c r="D31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q31" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R31" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S31" s="50" t="s">
@@ -6065,52 +6042,52 @@
     </row>
     <row r="32" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="14"/>
-      <c r="D32" s="59" t="s">
+      <c r="D32" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="E32" s="59" t="s">
+      <c r="E32" s="43" t="s">
         <v>663</v>
       </c>
-      <c r="F32" s="59" t="s">
+      <c r="F32" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="G32" s="59" t="s">
+      <c r="G32" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="H32" s="59" t="s">
+      <c r="H32" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="I32" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="J32" s="59" t="s">
+      <c r="I32" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="J32" s="43" t="s">
         <v>658</v>
       </c>
-      <c r="K32" s="59" t="s">
+      <c r="K32" s="43" t="s">
         <v>387</v>
       </c>
-      <c r="L32" s="59" t="s">
+      <c r="L32" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="M32" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N32" s="59" t="s">
+      <c r="M32" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N32" s="43" t="s">
         <v>665</v>
       </c>
-      <c r="O32" s="59" t="s">
+      <c r="O32" s="43" t="s">
         <v>839</v>
       </c>
-      <c r="P32" s="59" t="s">
+      <c r="P32" s="43" t="s">
         <v>667</v>
       </c>
-      <c r="Q32" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="R32" s="59" t="s">
+      <c r="Q32" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="R32" s="43" t="s">
         <v>670</v>
       </c>
-      <c r="S32" s="62" t="s">
+      <c r="S32" s="46" t="s">
         <v>156</v>
       </c>
       <c r="U32" s="26" t="str">
@@ -6124,104 +6101,104 @@
         <f>B29+1</f>
         <v>8</v>
       </c>
-      <c r="D33" s="57" t="s">
+      <c r="D33" s="51" t="s">
         <v>473</v>
       </c>
-      <c r="E33" s="57" t="s">
+      <c r="E33" s="51" t="s">
         <v>475</v>
       </c>
-      <c r="F33" s="57" t="s">
+      <c r="F33" s="51" t="s">
         <v>476</v>
       </c>
-      <c r="G33" s="57" t="s">
+      <c r="G33" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="H33" s="57" t="s">
+      <c r="H33" s="51" t="s">
         <v>220</v>
       </c>
-      <c r="I33" s="57" t="s">
+      <c r="I33" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="J33" s="57" t="s">
+      <c r="J33" s="51" t="s">
         <v>469</v>
       </c>
-      <c r="K33" s="57" t="s">
+      <c r="K33" s="51" t="s">
         <v>269</v>
       </c>
-      <c r="L33" s="57" t="s">
+      <c r="L33" s="51" t="s">
         <v>478</v>
       </c>
-      <c r="M33" s="57" t="s">
+      <c r="M33" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="N33" s="57" t="s">
+      <c r="N33" s="51" t="s">
         <v>479</v>
       </c>
-      <c r="O33" s="57" t="s">
+      <c r="O33" s="51" t="s">
         <v>471</v>
       </c>
-      <c r="P33" s="57" t="s">
+      <c r="P33" s="51" t="s">
         <v>480</v>
       </c>
-      <c r="Q33" s="57" t="s">
+      <c r="Q33" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="R33" s="57" t="s">
+      <c r="R33" s="51" t="s">
         <v>482</v>
       </c>
-      <c r="S33" s="61" t="s">
+      <c r="S33" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V33" s="55"/>
     </row>
     <row r="34" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="16"/>
-      <c r="D34" s="59" t="s">
+      <c r="D34" s="43" t="s">
         <v>330</v>
       </c>
-      <c r="E34" s="59" t="s">
+      <c r="E34" s="43" t="s">
         <v>663</v>
       </c>
-      <c r="F34" s="59" t="s">
+      <c r="F34" s="43" t="s">
         <v>386</v>
       </c>
-      <c r="G34" s="59" t="s">
+      <c r="G34" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="H34" s="59" t="s">
+      <c r="H34" s="43" t="s">
         <v>285</v>
       </c>
-      <c r="I34" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="J34" s="59" t="s">
+      <c r="I34" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="J34" s="43" t="s">
         <v>659</v>
       </c>
-      <c r="K34" s="59" t="s">
+      <c r="K34" s="43" t="s">
         <v>388</v>
       </c>
-      <c r="L34" s="59" t="s">
+      <c r="L34" s="43" t="s">
         <v>664</v>
       </c>
-      <c r="M34" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N34" s="59" t="s">
+      <c r="M34" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N34" s="43" t="s">
         <v>666</v>
       </c>
-      <c r="O34" s="59" t="s">
+      <c r="O34" s="43" t="s">
         <v>278</v>
       </c>
-      <c r="P34" s="59" t="s">
+      <c r="P34" s="43" t="s">
         <v>668</v>
       </c>
-      <c r="Q34" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="R34" s="60" t="s">
+      <c r="Q34" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="R34" s="44" t="s">
         <v>670</v>
       </c>
-      <c r="S34" s="63" t="s">
+      <c r="S34" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V34" s="55"/>
@@ -6229,49 +6206,49 @@
     <row r="35" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B35" s="10"/>
       <c r="C35" s="25"/>
-      <c r="D35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q35" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R35" s="58" t="s">
+      <c r="D35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q35" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R35" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S35" s="50" t="s">
@@ -6281,52 +6258,52 @@
     </row>
     <row r="36" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="14"/>
-      <c r="D36" s="59" t="s">
+      <c r="D36" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="E36" s="59" t="s">
+      <c r="E36" s="43" t="s">
         <v>672</v>
       </c>
-      <c r="F36" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="G36" s="59" t="s">
+      <c r="F36" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G36" s="43" t="s">
         <v>396</v>
       </c>
-      <c r="H36" s="59" t="s">
+      <c r="H36" s="43" t="s">
         <v>673</v>
       </c>
-      <c r="I36" s="59" t="s">
+      <c r="I36" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="J36" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="K36" s="59" t="s">
+      <c r="J36" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="K36" s="43" t="s">
         <v>652</v>
       </c>
-      <c r="L36" s="59" t="s">
+      <c r="L36" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="M36" s="59" t="s">
+      <c r="M36" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="N36" s="59" t="s">
+      <c r="N36" s="43" t="s">
         <v>308</v>
       </c>
-      <c r="O36" s="59" t="s">
+      <c r="O36" s="43" t="s">
         <v>635</v>
       </c>
-      <c r="P36" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q36" s="59" t="s">
+      <c r="P36" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q36" s="43" t="s">
         <v>675</v>
       </c>
-      <c r="R36" s="59" t="s">
+      <c r="R36" s="43" t="s">
         <v>677</v>
       </c>
-      <c r="S36" s="62" t="s">
+      <c r="S36" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V36" s="55"/>
@@ -6336,104 +6313,104 @@
         <f>B33+1</f>
         <v>9</v>
       </c>
-      <c r="D37" s="57" t="s">
+      <c r="D37" s="51" t="s">
         <v>254</v>
       </c>
-      <c r="E37" s="57" t="s">
+      <c r="E37" s="51" t="s">
         <v>484</v>
       </c>
-      <c r="F37" s="57" t="s">
+      <c r="F37" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="G37" s="57" t="s">
+      <c r="G37" s="51" t="s">
         <v>485</v>
       </c>
-      <c r="H37" s="57" t="s">
+      <c r="H37" s="51" t="s">
         <v>486</v>
       </c>
-      <c r="I37" s="57" t="s">
+      <c r="I37" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="J37" s="57" t="s">
+      <c r="J37" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="K37" s="57" t="s">
+      <c r="K37" s="51" t="s">
         <v>465</v>
       </c>
-      <c r="L37" s="57" t="s">
+      <c r="L37" s="51" t="s">
         <v>439</v>
       </c>
-      <c r="M37" s="57" t="s">
+      <c r="M37" s="51" t="s">
         <v>256</v>
       </c>
-      <c r="N37" s="57" t="s">
+      <c r="N37" s="51" t="s">
         <v>226</v>
       </c>
-      <c r="O37" s="57" t="s">
+      <c r="O37" s="51" t="s">
         <v>450</v>
       </c>
-      <c r="P37" s="57" t="s">
+      <c r="P37" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="Q37" s="57" t="s">
+      <c r="Q37" s="51" t="s">
         <v>488</v>
       </c>
-      <c r="R37" s="57" t="s">
+      <c r="R37" s="51" t="s">
         <v>489</v>
       </c>
-      <c r="S37" s="61" t="s">
+      <c r="S37" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V37" s="55"/>
     </row>
     <row r="38" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="16"/>
-      <c r="D38" s="59" t="s">
+      <c r="D38" s="43" t="s">
         <v>367</v>
       </c>
-      <c r="E38" s="59" t="s">
+      <c r="E38" s="43" t="s">
         <v>672</v>
       </c>
-      <c r="F38" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="G38" s="59" t="s">
+      <c r="F38" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G38" s="43" t="s">
         <v>318</v>
       </c>
-      <c r="H38" s="59" t="s">
+      <c r="H38" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="I38" s="59" t="s">
+      <c r="I38" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="J38" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="K38" s="59" t="s">
+      <c r="J38" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="K38" s="43" t="s">
         <v>652</v>
       </c>
-      <c r="L38" s="59" t="s">
+      <c r="L38" s="43" t="s">
         <v>206</v>
       </c>
-      <c r="M38" s="59" t="s">
+      <c r="M38" s="43" t="s">
         <v>201</v>
       </c>
-      <c r="N38" s="59" t="s">
+      <c r="N38" s="43" t="s">
         <v>308</v>
       </c>
-      <c r="O38" s="59" t="s">
+      <c r="O38" s="43" t="s">
         <v>636</v>
       </c>
-      <c r="P38" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q38" s="60" t="s">
+      <c r="P38" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q38" s="44" t="s">
         <v>676</v>
       </c>
-      <c r="R38" s="60" t="s">
+      <c r="R38" s="44" t="s">
         <v>678</v>
       </c>
-      <c r="S38" s="63" t="s">
+      <c r="S38" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V38" s="55"/>
@@ -6441,49 +6418,49 @@
     <row r="39" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B39" s="10"/>
       <c r="C39" s="25"/>
-      <c r="D39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q39" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R39" s="58" t="s">
+      <c r="D39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q39" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R39" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S39" s="50" t="s">
@@ -6493,52 +6470,52 @@
     </row>
     <row r="40" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="14"/>
-      <c r="D40" s="59" t="s">
+      <c r="D40" s="43" t="s">
         <v>680</v>
       </c>
-      <c r="E40" s="59" t="s">
+      <c r="E40" s="43" t="s">
         <v>682</v>
       </c>
-      <c r="F40" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="G40" s="59" t="s">
+      <c r="F40" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G40" s="43" t="s">
         <v>684</v>
       </c>
-      <c r="H40" s="59" t="s">
+      <c r="H40" s="43" t="s">
         <v>283</v>
       </c>
-      <c r="I40" s="59" t="s">
+      <c r="I40" s="43" t="s">
         <v>356</v>
       </c>
-      <c r="J40" s="59" t="s">
+      <c r="J40" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="K40" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="L40" s="59" t="s">
+      <c r="K40" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="L40" s="43" t="s">
         <v>686</v>
       </c>
-      <c r="M40" s="59" t="s">
+      <c r="M40" s="43" t="s">
         <v>387</v>
       </c>
-      <c r="N40" s="59" t="s">
+      <c r="N40" s="43" t="s">
         <v>327</v>
       </c>
-      <c r="O40" s="59" t="s">
+      <c r="O40" s="43" t="s">
         <v>677</v>
       </c>
-      <c r="P40" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q40" s="59" t="s">
+      <c r="P40" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q40" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="R40" s="59" t="s">
+      <c r="R40" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="S40" s="62" t="s">
+      <c r="S40" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V40" s="55"/>
@@ -6548,104 +6525,104 @@
         <f>B37+1</f>
         <v>10</v>
       </c>
-      <c r="D41" s="57" t="s">
+      <c r="D41" s="51" t="s">
         <v>491</v>
       </c>
-      <c r="E41" s="57" t="s">
+      <c r="E41" s="51" t="s">
         <v>493</v>
       </c>
-      <c r="F41" s="57" t="s">
+      <c r="F41" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="G41" s="57" t="s">
+      <c r="G41" s="51" t="s">
         <v>494</v>
       </c>
-      <c r="H41" s="57" t="s">
+      <c r="H41" s="51" t="s">
         <v>219</v>
       </c>
-      <c r="I41" s="57" t="s">
+      <c r="I41" s="51" t="s">
         <v>495</v>
       </c>
-      <c r="J41" s="57" t="s">
+      <c r="J41" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="K41" s="57" t="s">
+      <c r="K41" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="L41" s="57" t="s">
+      <c r="L41" s="51" t="s">
         <v>496</v>
       </c>
-      <c r="M41" s="57" t="s">
+      <c r="M41" s="51" t="s">
         <v>269</v>
       </c>
-      <c r="N41" s="57" t="s">
+      <c r="N41" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="O41" s="57" t="s">
+      <c r="O41" s="51" t="s">
         <v>489</v>
       </c>
-      <c r="P41" s="57" t="s">
+      <c r="P41" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="Q41" s="57" t="s">
+      <c r="Q41" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="R41" s="57" t="s">
+      <c r="R41" s="51" t="s">
         <v>497</v>
       </c>
-      <c r="S41" s="61" t="s">
+      <c r="S41" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V41" s="55"/>
     </row>
     <row r="42" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="16"/>
-      <c r="D42" s="59" t="s">
+      <c r="D42" s="43" t="s">
         <v>681</v>
       </c>
-      <c r="E42" s="59" t="s">
+      <c r="E42" s="43" t="s">
         <v>683</v>
       </c>
-      <c r="F42" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="G42" s="59" t="s">
+      <c r="F42" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G42" s="43" t="s">
         <v>685</v>
       </c>
-      <c r="H42" s="59" t="s">
+      <c r="H42" s="43" t="s">
         <v>284</v>
       </c>
-      <c r="I42" s="59" t="s">
+      <c r="I42" s="43" t="s">
         <v>357</v>
       </c>
-      <c r="J42" s="59" t="s">
+      <c r="J42" s="43" t="s">
         <v>342</v>
       </c>
-      <c r="K42" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="L42" s="59" t="s">
+      <c r="K42" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="L42" s="43" t="s">
         <v>687</v>
       </c>
-      <c r="M42" s="59" t="s">
+      <c r="M42" s="43" t="s">
         <v>388</v>
       </c>
-      <c r="N42" s="59" t="s">
+      <c r="N42" s="43" t="s">
         <v>328</v>
       </c>
-      <c r="O42" s="59" t="s">
+      <c r="O42" s="43" t="s">
         <v>678</v>
       </c>
-      <c r="P42" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q42" s="60" t="s">
+      <c r="P42" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q42" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="R42" s="60" t="s">
+      <c r="R42" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="S42" s="63" t="s">
+      <c r="S42" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V42" s="55"/>
@@ -6653,49 +6630,49 @@
     <row r="43" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B43" s="10"/>
       <c r="C43" s="25"/>
-      <c r="D43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q43" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R43" s="58" t="s">
+      <c r="D43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q43" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R43" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S43" s="50" t="s">
@@ -6705,52 +6682,52 @@
     </row>
     <row r="44" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="14"/>
-      <c r="D44" s="59" t="s">
+      <c r="D44" s="43" t="s">
         <v>842</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="43" t="s">
         <v>303</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="G44" s="59" t="s">
+      <c r="G44" s="43" t="s">
         <v>314</v>
       </c>
-      <c r="H44" s="59" t="s">
+      <c r="H44" s="43" t="s">
         <v>203</v>
       </c>
-      <c r="I44" s="59" t="s">
+      <c r="I44" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="J44" s="59" t="s">
+      <c r="J44" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="K44" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="L44" s="59" t="s">
+      <c r="K44" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="L44" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="M44" s="59" t="s">
+      <c r="M44" s="43" t="s">
         <v>198</v>
       </c>
-      <c r="N44" s="59" t="s">
+      <c r="N44" s="43" t="s">
         <v>296</v>
       </c>
-      <c r="O44" s="59" t="s">
+      <c r="O44" s="43" t="s">
         <v>673</v>
       </c>
-      <c r="P44" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q44" s="59" t="s">
+      <c r="P44" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q44" s="43" t="s">
         <v>690</v>
       </c>
-      <c r="R44" s="59" t="s">
+      <c r="R44" s="43" t="s">
         <v>693</v>
       </c>
-      <c r="S44" s="62" t="s">
+      <c r="S44" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V44" s="55"/>
@@ -6760,104 +6737,104 @@
         <f>B41+1</f>
         <v>11</v>
       </c>
-      <c r="D45" s="57" t="s">
+      <c r="D45" s="51" t="s">
         <v>499</v>
       </c>
-      <c r="E45" s="57" t="s">
+      <c r="E45" s="51" t="s">
         <v>225</v>
       </c>
-      <c r="F45" s="57" t="s">
+      <c r="F45" s="51" t="s">
         <v>501</v>
       </c>
-      <c r="G45" s="57" t="s">
+      <c r="G45" s="51" t="s">
         <v>266</v>
       </c>
-      <c r="H45" s="57" t="s">
+      <c r="H45" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="I45" s="57" t="s">
+      <c r="I45" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="J45" s="57" t="s">
+      <c r="J45" s="51" t="s">
         <v>237</v>
       </c>
-      <c r="K45" s="57" t="s">
+      <c r="K45" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="L45" s="57" t="s">
+      <c r="L45" s="51" t="s">
         <v>503</v>
       </c>
-      <c r="M45" s="57" t="s">
+      <c r="M45" s="51" t="s">
         <v>505</v>
       </c>
-      <c r="N45" s="57" t="s">
+      <c r="N45" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="O45" s="57" t="s">
+      <c r="O45" s="51" t="s">
         <v>486</v>
       </c>
-      <c r="P45" s="57" t="s">
+      <c r="P45" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="Q45" s="57" t="s">
+      <c r="Q45" s="51" t="s">
         <v>506</v>
       </c>
-      <c r="R45" s="57" t="s">
+      <c r="R45" s="51" t="s">
         <v>508</v>
       </c>
-      <c r="S45" s="61" t="s">
+      <c r="S45" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V45" s="55"/>
     </row>
     <row r="46" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="16"/>
-      <c r="D46" s="59" t="s">
+      <c r="D46" s="43" t="s">
         <v>843</v>
       </c>
-      <c r="E46" s="59" t="s">
+      <c r="E46" s="43" t="s">
         <v>304</v>
       </c>
-      <c r="F46" s="59" t="s">
+      <c r="F46" s="43" t="s">
         <v>293</v>
       </c>
-      <c r="G46" s="59" t="s">
+      <c r="G46" s="43" t="s">
         <v>314</v>
       </c>
-      <c r="H46" s="59" t="s">
+      <c r="H46" s="43" t="s">
         <v>204</v>
       </c>
-      <c r="I46" s="59" t="s">
+      <c r="I46" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="J46" s="59" t="s">
+      <c r="J46" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="K46" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="L46" s="59" t="s">
+      <c r="K46" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="L46" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="M46" s="59" t="s">
+      <c r="M46" s="43" t="s">
         <v>689</v>
       </c>
-      <c r="N46" s="59" t="s">
+      <c r="N46" s="43" t="s">
         <v>297</v>
       </c>
-      <c r="O46" s="59" t="s">
+      <c r="O46" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="P46" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q46" s="60" t="s">
+      <c r="P46" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q46" s="44" t="s">
         <v>691</v>
       </c>
-      <c r="R46" s="60" t="s">
+      <c r="R46" s="44" t="s">
         <v>376</v>
       </c>
-      <c r="S46" s="63" t="s">
+      <c r="S46" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V46" s="55"/>
@@ -6865,49 +6842,49 @@
     <row r="47" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B47" s="10"/>
       <c r="C47" s="25"/>
-      <c r="D47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q47" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R47" s="58" t="s">
+      <c r="D47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q47" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R47" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S47" s="50" t="s">
@@ -6917,52 +6894,52 @@
     </row>
     <row r="48" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B48" s="14"/>
-      <c r="D48" s="59" t="s">
+      <c r="D48" s="43" t="s">
         <v>375</v>
       </c>
-      <c r="E48" s="59" t="s">
+      <c r="E48" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="F48" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="G48" s="59" t="s">
+      <c r="F48" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G48" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="H48" s="59" t="s">
+      <c r="H48" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="I48" s="59" t="s">
+      <c r="I48" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="J48" s="59" t="s">
+      <c r="J48" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="K48" s="59" t="s">
+      <c r="K48" s="43" t="s">
         <v>695</v>
       </c>
-      <c r="L48" s="59" t="s">
+      <c r="L48" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="M48" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N48" s="59" t="s">
+      <c r="M48" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N48" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="O48" s="59" t="s">
+      <c r="O48" s="43" t="s">
         <v>347</v>
       </c>
-      <c r="P48" s="59" t="s">
+      <c r="P48" s="43" t="s">
         <v>698</v>
       </c>
-      <c r="Q48" s="59" t="s">
+      <c r="Q48" s="43" t="s">
         <v>844</v>
       </c>
-      <c r="R48" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="S48" s="62" t="s">
+      <c r="R48" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="S48" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V48" s="55"/>
@@ -6972,104 +6949,104 @@
         <f>B45+1</f>
         <v>12</v>
       </c>
-      <c r="D49" s="57" t="s">
+      <c r="D49" s="51" t="s">
         <v>259</v>
       </c>
-      <c r="E49" s="57" t="s">
+      <c r="E49" s="51" t="s">
         <v>509</v>
       </c>
-      <c r="F49" s="57" t="s">
+      <c r="F49" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="G49" s="57" t="s">
+      <c r="G49" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="H49" s="57" t="s">
+      <c r="H49" s="51" t="s">
         <v>253</v>
       </c>
-      <c r="I49" s="57" t="s">
+      <c r="I49" s="51" t="s">
         <v>510</v>
       </c>
-      <c r="J49" s="57" t="s">
+      <c r="J49" s="51" t="s">
         <v>168</v>
       </c>
-      <c r="K49" s="57" t="s">
+      <c r="K49" s="51" t="s">
         <v>512</v>
       </c>
-      <c r="L49" s="57" t="s">
+      <c r="L49" s="51" t="s">
         <v>232</v>
       </c>
-      <c r="M49" s="57" t="s">
+      <c r="M49" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="N49" s="57" t="s">
+      <c r="N49" s="51" t="s">
         <v>514</v>
       </c>
-      <c r="O49" s="57" t="s">
+      <c r="O49" s="51" t="s">
         <v>516</v>
       </c>
-      <c r="P49" s="57" t="s">
+      <c r="P49" s="51" t="s">
         <v>518</v>
       </c>
-      <c r="Q49" s="57" t="s">
+      <c r="Q49" s="51" t="s">
         <v>519</v>
       </c>
-      <c r="R49" s="57" t="s">
+      <c r="R49" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="S49" s="61" t="s">
+      <c r="S49" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V49" s="55"/>
     </row>
     <row r="50" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="16"/>
-      <c r="D50" s="59" t="s">
+      <c r="D50" s="43" t="s">
         <v>375</v>
       </c>
-      <c r="E50" s="59" t="s">
+      <c r="E50" s="43" t="s">
         <v>307</v>
       </c>
-      <c r="F50" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="G50" s="59" t="s">
+      <c r="F50" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G50" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="H50" s="59" t="s">
+      <c r="H50" s="43" t="s">
         <v>366</v>
       </c>
-      <c r="I50" s="59" t="s">
+      <c r="I50" s="43" t="s">
         <v>694</v>
       </c>
-      <c r="J50" s="59" t="s">
+      <c r="J50" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="K50" s="59" t="s">
+      <c r="K50" s="43" t="s">
         <v>665</v>
       </c>
-      <c r="L50" s="59" t="s">
+      <c r="L50" s="43" t="s">
         <v>317</v>
       </c>
-      <c r="M50" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N50" s="59" t="s">
+      <c r="M50" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N50" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="O50" s="59" t="s">
+      <c r="O50" s="43" t="s">
         <v>697</v>
       </c>
-      <c r="P50" s="59" t="s">
+      <c r="P50" s="43" t="s">
         <v>699</v>
       </c>
-      <c r="Q50" s="60" t="s">
+      <c r="Q50" s="44" t="s">
         <v>845</v>
       </c>
-      <c r="R50" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="S50" s="63" t="s">
+      <c r="R50" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="S50" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V50" s="55"/>
@@ -7077,49 +7054,49 @@
     <row r="51" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B51" s="10"/>
       <c r="C51" s="25"/>
-      <c r="D51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q51" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R51" s="58" t="s">
+      <c r="D51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q51" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R51" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S51" s="50" t="s">
@@ -7129,52 +7106,52 @@
     </row>
     <row r="52" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="14"/>
-      <c r="D52" s="59" t="s">
+      <c r="D52" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="E52" s="59" t="s">
+      <c r="E52" s="43" t="s">
         <v>193</v>
       </c>
-      <c r="F52" s="59" t="s">
+      <c r="F52" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="G52" s="59" t="s">
+      <c r="G52" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="H52" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I52" s="59" t="s">
+      <c r="H52" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I52" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="J52" s="59" t="s">
+      <c r="J52" s="43" t="s">
         <v>359</v>
       </c>
-      <c r="K52" s="59" t="s">
+      <c r="K52" s="43" t="s">
         <v>374</v>
       </c>
-      <c r="L52" s="59" t="s">
+      <c r="L52" s="43" t="s">
         <v>700</v>
       </c>
-      <c r="M52" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N52" s="59" t="s">
+      <c r="M52" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N52" s="43" t="s">
         <v>365</v>
       </c>
-      <c r="O52" s="59" t="s">
+      <c r="O52" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="P52" s="59" t="s">
+      <c r="P52" s="43" t="s">
         <v>677</v>
       </c>
-      <c r="Q52" s="59" t="s">
+      <c r="Q52" s="43" t="s">
         <v>371</v>
       </c>
-      <c r="R52" s="59" t="s">
+      <c r="R52" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="S52" s="62" t="s">
+      <c r="S52" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V52" s="55"/>
@@ -7184,104 +7161,104 @@
         <f>B49+1</f>
         <v>13</v>
       </c>
-      <c r="D53" s="57" t="s">
+      <c r="D53" s="51" t="s">
         <v>521</v>
       </c>
-      <c r="E53" s="57" t="s">
+      <c r="E53" s="51" t="s">
         <v>227</v>
       </c>
-      <c r="F53" s="57" t="s">
+      <c r="F53" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="G53" s="57" t="s">
+      <c r="G53" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="H53" s="57" t="s">
+      <c r="H53" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="I53" s="57" t="s">
+      <c r="I53" s="51" t="s">
         <v>246</v>
       </c>
-      <c r="J53" s="57" t="s">
+      <c r="J53" s="51" t="s">
         <v>523</v>
       </c>
-      <c r="K53" s="57" t="s">
+      <c r="K53" s="51" t="s">
         <v>525</v>
       </c>
-      <c r="L53" s="57" t="s">
+      <c r="L53" s="51" t="s">
         <v>527</v>
       </c>
-      <c r="M53" s="57" t="s">
+      <c r="M53" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="N53" s="57" t="s">
+      <c r="N53" s="51" t="s">
         <v>529</v>
       </c>
-      <c r="O53" s="57" t="s">
+      <c r="O53" s="51" t="s">
         <v>531</v>
       </c>
-      <c r="P53" s="57" t="s">
+      <c r="P53" s="51" t="s">
         <v>489</v>
       </c>
-      <c r="Q53" s="57" t="s">
+      <c r="Q53" s="51" t="s">
         <v>274</v>
       </c>
-      <c r="R53" s="57" t="s">
+      <c r="R53" s="51" t="s">
         <v>532</v>
       </c>
-      <c r="S53" s="61" t="s">
+      <c r="S53" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V53" s="55"/>
     </row>
     <row r="54" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="16"/>
-      <c r="D54" s="59" t="s">
+      <c r="D54" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="E54" s="59" t="s">
+      <c r="E54" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="F54" s="59" t="s">
+      <c r="F54" s="43" t="s">
         <v>401</v>
       </c>
-      <c r="G54" s="59" t="s">
+      <c r="G54" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="H54" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I54" s="59" t="s">
+      <c r="H54" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I54" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="J54" s="59" t="s">
+      <c r="J54" s="43" t="s">
         <v>360</v>
       </c>
-      <c r="K54" s="59" t="s">
+      <c r="K54" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="L54" s="59" t="s">
+      <c r="L54" s="43" t="s">
         <v>701</v>
       </c>
-      <c r="M54" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N54" s="59" t="s">
+      <c r="M54" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N54" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="O54" s="59" t="s">
+      <c r="O54" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="P54" s="59" t="s">
+      <c r="P54" s="43" t="s">
         <v>678</v>
       </c>
-      <c r="Q54" s="60" t="s">
+      <c r="Q54" s="44" t="s">
         <v>372</v>
       </c>
-      <c r="R54" s="60" t="s">
+      <c r="R54" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="S54" s="63" t="s">
+      <c r="S54" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V54" s="55"/>
@@ -7289,10 +7266,10 @@
     <row r="55" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B55" s="10"/>
       <c r="C55" s="25"/>
-      <c r="D55" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E55" s="58" t="s">
+      <c r="D55" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E55" s="41" t="s">
         <v>156</v>
       </c>
       <c r="F55" s="41" t="s">
@@ -7341,10 +7318,10 @@
     </row>
     <row r="56" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="14"/>
-      <c r="D56" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="E56" s="59" t="s">
+      <c r="D56" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="E56" s="43" t="s">
         <v>156</v>
       </c>
       <c r="F56" s="43" t="s">
@@ -7396,10 +7373,10 @@
         <f>B53+1</f>
         <v>14</v>
       </c>
-      <c r="D57" s="57" t="s">
+      <c r="D57" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="E57" s="57" t="str">
+      <c r="E57" s="51" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -7450,10 +7427,10 @@
     </row>
     <row r="58" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="16"/>
-      <c r="D58" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="E58" s="59" t="s">
+      <c r="D58" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="E58" s="43" t="s">
         <v>156</v>
       </c>
       <c r="F58" s="43" t="s">
@@ -7503,49 +7480,49 @@
     <row r="59" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B59" s="10"/>
       <c r="C59" s="25"/>
-      <c r="D59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q59" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R59" s="58" t="s">
+      <c r="D59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q59" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R59" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S59" s="50" t="s">
@@ -7555,52 +7532,52 @@
     </row>
     <row r="60" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="14"/>
-      <c r="D60" s="59" t="s">
+      <c r="D60" s="43" t="s">
         <v>376</v>
       </c>
-      <c r="E60" s="59" t="s">
+      <c r="E60" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="F60" s="59" t="s">
+      <c r="F60" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="G60" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="H60" s="59" t="s">
+      <c r="G60" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="H60" s="43" t="s">
         <v>702</v>
       </c>
-      <c r="I60" s="59" t="s">
+      <c r="I60" s="43" t="s">
         <v>704</v>
       </c>
-      <c r="J60" s="59" t="s">
+      <c r="J60" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="K60" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="L60" s="59" t="s">
+      <c r="K60" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="L60" s="43" t="s">
         <v>707</v>
       </c>
-      <c r="M60" s="59" t="s">
+      <c r="M60" s="43" t="s">
         <v>379</v>
       </c>
-      <c r="N60" s="59" t="s">
+      <c r="N60" s="43" t="s">
         <v>665</v>
       </c>
-      <c r="O60" s="59" t="s">
+      <c r="O60" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="P60" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q60" s="59" t="s">
+      <c r="P60" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q60" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="R60" s="59" t="s">
+      <c r="R60" s="43" t="s">
         <v>710</v>
       </c>
-      <c r="S60" s="62" t="s">
+      <c r="S60" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V60" s="55"/>
@@ -7610,104 +7587,104 @@
         <f>B57+1</f>
         <v>15</v>
       </c>
-      <c r="D61" s="57" t="s">
+      <c r="D61" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="E61" s="57" t="s">
+      <c r="E61" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="F61" s="57" t="s">
+      <c r="F61" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="G61" s="57" t="s">
+      <c r="G61" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="H61" s="57" t="s">
+      <c r="H61" s="51" t="s">
         <v>533</v>
       </c>
-      <c r="I61" s="57" t="s">
+      <c r="I61" s="51" t="s">
         <v>534</v>
       </c>
-      <c r="J61" s="57" t="s">
+      <c r="J61" s="51" t="s">
         <v>251</v>
       </c>
-      <c r="K61" s="57" t="s">
+      <c r="K61" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="L61" s="57" t="s">
+      <c r="L61" s="51" t="s">
         <v>536</v>
       </c>
-      <c r="M61" s="57" t="s">
+      <c r="M61" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="N61" s="57" t="s">
+      <c r="N61" s="51" t="s">
         <v>479</v>
       </c>
-      <c r="O61" s="57" t="s">
+      <c r="O61" s="51" t="s">
         <v>168</v>
       </c>
-      <c r="P61" s="57" t="s">
+      <c r="P61" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="Q61" s="57" t="s">
+      <c r="Q61" s="51" t="s">
         <v>252</v>
       </c>
-      <c r="R61" s="57" t="s">
+      <c r="R61" s="51" t="s">
         <v>538</v>
       </c>
-      <c r="S61" s="61" t="s">
+      <c r="S61" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V61" s="55"/>
     </row>
     <row r="62" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="16"/>
-      <c r="D62" s="59" t="s">
+      <c r="D62" s="43" t="s">
         <v>377</v>
       </c>
-      <c r="E62" s="59" t="s">
+      <c r="E62" s="43" t="s">
         <v>286</v>
       </c>
-      <c r="F62" s="59" t="s">
+      <c r="F62" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="G62" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="H62" s="59" t="s">
+      <c r="G62" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="H62" s="43" t="s">
         <v>703</v>
       </c>
-      <c r="I62" s="59" t="s">
+      <c r="I62" s="43" t="s">
         <v>705</v>
       </c>
-      <c r="J62" s="59" t="s">
+      <c r="J62" s="43" t="s">
         <v>216</v>
       </c>
-      <c r="K62" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="L62" s="59" t="s">
+      <c r="K62" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="L62" s="43" t="s">
         <v>708</v>
       </c>
-      <c r="M62" s="59" t="s">
+      <c r="M62" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="N62" s="59" t="s">
+      <c r="N62" s="43" t="s">
         <v>666</v>
       </c>
-      <c r="O62" s="59" t="s">
+      <c r="O62" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="P62" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q62" s="60" t="s">
+      <c r="P62" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q62" s="44" t="s">
         <v>364</v>
       </c>
-      <c r="R62" s="60" t="s">
+      <c r="R62" s="44" t="s">
         <v>711</v>
       </c>
-      <c r="S62" s="63" t="s">
+      <c r="S62" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V62" s="55"/>
@@ -7715,49 +7692,49 @@
     <row r="63" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B63" s="10"/>
       <c r="C63" s="25"/>
-      <c r="D63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q63" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R63" s="58" t="s">
+      <c r="D63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q63" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R63" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S63" s="50" t="s">
@@ -7767,52 +7744,52 @@
     </row>
     <row r="64" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B64" s="14"/>
-      <c r="D64" s="59" t="s">
+      <c r="D64" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E64" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="F64" s="59" t="s">
+      <c r="E64" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="F64" s="43" t="s">
         <v>658</v>
       </c>
-      <c r="G64" s="59" t="s">
+      <c r="G64" s="43" t="s">
         <v>846</v>
       </c>
-      <c r="H64" s="59" t="s">
+      <c r="H64" s="43" t="s">
         <v>408</v>
       </c>
-      <c r="I64" s="59" t="s">
+      <c r="I64" s="43" t="s">
         <v>296</v>
       </c>
-      <c r="J64" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="K64" s="59" t="s">
+      <c r="J64" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="K64" s="43" t="s">
         <v>715</v>
       </c>
-      <c r="L64" s="59" t="s">
+      <c r="L64" s="43" t="s">
         <v>718</v>
       </c>
-      <c r="M64" s="59" t="s">
+      <c r="M64" s="43" t="s">
         <v>720</v>
       </c>
-      <c r="N64" s="59" t="s">
+      <c r="N64" s="43" t="s">
         <v>690</v>
       </c>
-      <c r="O64" s="59" t="s">
+      <c r="O64" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="P64" s="59" t="s">
+      <c r="P64" s="43" t="s">
         <v>349</v>
       </c>
-      <c r="Q64" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="R64" s="59" t="s">
+      <c r="Q64" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="R64" s="43" t="s">
         <v>344</v>
       </c>
-      <c r="S64" s="62" t="s">
+      <c r="S64" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V64" s="55"/>
@@ -7822,104 +7799,104 @@
         <f>B61+1</f>
         <v>16</v>
       </c>
-      <c r="D65" s="57" t="s">
+      <c r="D65" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="E65" s="57" t="s">
+      <c r="E65" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="F65" s="57" t="s">
+      <c r="F65" s="51" t="s">
         <v>469</v>
       </c>
-      <c r="G65" s="57" t="s">
+      <c r="G65" s="51" t="s">
         <v>540</v>
       </c>
-      <c r="H65" s="57" t="s">
+      <c r="H65" s="51" t="s">
         <v>542</v>
       </c>
-      <c r="I65" s="57" t="s">
+      <c r="I65" s="51" t="s">
         <v>231</v>
       </c>
-      <c r="J65" s="57" t="s">
+      <c r="J65" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="K65" s="57" t="s">
+      <c r="K65" s="51" t="s">
         <v>544</v>
       </c>
-      <c r="L65" s="57" t="s">
+      <c r="L65" s="51" t="s">
         <v>546</v>
       </c>
-      <c r="M65" s="57" t="s">
+      <c r="M65" s="51" t="s">
         <v>547</v>
       </c>
-      <c r="N65" s="57" t="s">
+      <c r="N65" s="51" t="s">
         <v>506</v>
       </c>
-      <c r="O65" s="57" t="s">
+      <c r="O65" s="51" t="s">
         <v>232</v>
       </c>
-      <c r="P65" s="57" t="s">
+      <c r="P65" s="51" t="s">
         <v>244</v>
       </c>
-      <c r="Q65" s="57" t="s">
+      <c r="Q65" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="R65" s="57" t="s">
+      <c r="R65" s="51" t="s">
         <v>549</v>
       </c>
-      <c r="S65" s="61" t="s">
+      <c r="S65" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V65" s="55"/>
     </row>
     <row r="66" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B66" s="16"/>
-      <c r="D66" s="59" t="s">
+      <c r="D66" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E66" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="F66" s="59" t="s">
+      <c r="E66" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="F66" s="43" t="s">
         <v>659</v>
       </c>
-      <c r="G66" s="59" t="s">
+      <c r="G66" s="43" t="s">
         <v>847</v>
       </c>
-      <c r="H66" s="59" t="s">
+      <c r="H66" s="43" t="s">
         <v>713</v>
       </c>
-      <c r="I66" s="59" t="s">
+      <c r="I66" s="43" t="s">
         <v>297</v>
       </c>
-      <c r="J66" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="K66" s="59" t="s">
+      <c r="J66" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="K66" s="43" t="s">
         <v>716</v>
       </c>
-      <c r="L66" s="59" t="s">
+      <c r="L66" s="43" t="s">
         <v>719</v>
       </c>
-      <c r="M66" s="59" t="s">
+      <c r="M66" s="43" t="s">
         <v>721</v>
       </c>
-      <c r="N66" s="59" t="s">
+      <c r="N66" s="43" t="s">
         <v>691</v>
       </c>
-      <c r="O66" s="59" t="s">
+      <c r="O66" s="43" t="s">
         <v>317</v>
       </c>
-      <c r="P66" s="59" t="s">
+      <c r="P66" s="43" t="s">
         <v>349</v>
       </c>
-      <c r="Q66" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="R66" s="60" t="s">
+      <c r="Q66" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="R66" s="44" t="s">
         <v>344</v>
       </c>
-      <c r="S66" s="63" t="s">
+      <c r="S66" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V66" s="55"/>
@@ -7927,49 +7904,49 @@
     <row r="67" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B67" s="10"/>
       <c r="C67" s="25"/>
-      <c r="D67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q67" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R67" s="58" t="s">
+      <c r="D67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q67" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R67" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S67" s="50" t="s">
@@ -7979,52 +7956,52 @@
     </row>
     <row r="68" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="14"/>
-      <c r="D68" s="59" t="s">
+      <c r="D68" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="E68" s="59" t="s">
+      <c r="E68" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="F68" s="59" t="s">
+      <c r="F68" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="G68" s="59" t="s">
+      <c r="G68" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="H68" s="59" t="s">
+      <c r="H68" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="I68" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="J68" s="59" t="s">
+      <c r="I68" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="J68" s="43" t="s">
         <v>851</v>
       </c>
-      <c r="K68" s="59" t="s">
+      <c r="K68" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="L68" s="59" t="s">
+      <c r="L68" s="43" t="s">
         <v>707</v>
       </c>
-      <c r="M68" s="59" t="s">
+      <c r="M68" s="43" t="s">
         <v>722</v>
       </c>
-      <c r="N68" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="O68" s="59" t="s">
+      <c r="N68" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="O68" s="43" t="s">
         <v>371</v>
       </c>
-      <c r="P68" s="59" t="s">
+      <c r="P68" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="Q68" s="59" t="s">
+      <c r="Q68" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="R68" s="59" t="s">
+      <c r="R68" s="43" t="s">
         <v>336</v>
       </c>
-      <c r="S68" s="62" t="s">
+      <c r="S68" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V68" s="55"/>
@@ -8034,104 +8011,104 @@
         <f>B65+1</f>
         <v>17</v>
       </c>
-      <c r="D69" s="57" t="s">
+      <c r="D69" s="51" t="s">
         <v>253</v>
       </c>
-      <c r="E69" s="57" t="s">
+      <c r="E69" s="51" t="s">
         <v>509</v>
       </c>
-      <c r="F69" s="57" t="s">
+      <c r="F69" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="G69" s="57" t="s">
+      <c r="G69" s="51" t="s">
         <v>550</v>
       </c>
-      <c r="H69" s="57" t="s">
+      <c r="H69" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="I69" s="57" t="s">
+      <c r="I69" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="J69" s="57" t="s">
+      <c r="J69" s="51" t="s">
         <v>849</v>
       </c>
-      <c r="K69" s="57" t="s">
+      <c r="K69" s="51" t="s">
         <v>168</v>
       </c>
-      <c r="L69" s="57" t="s">
+      <c r="L69" s="51" t="s">
         <v>536</v>
       </c>
-      <c r="M69" s="57" t="s">
+      <c r="M69" s="51" t="s">
         <v>552</v>
       </c>
-      <c r="N69" s="57" t="s">
+      <c r="N69" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="O69" s="57" t="s">
+      <c r="O69" s="51" t="s">
         <v>274</v>
       </c>
-      <c r="P69" s="57" t="s">
+      <c r="P69" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="Q69" s="57" t="s">
+      <c r="Q69" s="51" t="s">
         <v>553</v>
       </c>
-      <c r="R69" s="57" t="s">
+      <c r="R69" s="51" t="s">
         <v>554</v>
       </c>
-      <c r="S69" s="61" t="s">
+      <c r="S69" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V69" s="55"/>
     </row>
     <row r="70" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="16"/>
-      <c r="D70" s="59" t="s">
+      <c r="D70" s="43" t="s">
         <v>366</v>
       </c>
-      <c r="E70" s="59" t="s">
+      <c r="E70" s="43" t="s">
         <v>307</v>
       </c>
-      <c r="F70" s="59" t="s">
+      <c r="F70" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="G70" s="59" t="s">
+      <c r="G70" s="43" t="s">
         <v>381</v>
       </c>
-      <c r="H70" s="59" t="s">
+      <c r="H70" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="I70" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="J70" s="59" t="s">
+      <c r="I70" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="J70" s="43" t="s">
         <v>852</v>
       </c>
-      <c r="K70" s="59" t="s">
+      <c r="K70" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="L70" s="59" t="s">
+      <c r="L70" s="43" t="s">
         <v>708</v>
       </c>
-      <c r="M70" s="59" t="s">
+      <c r="M70" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="N70" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="O70" s="59" t="s">
+      <c r="N70" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="O70" s="43" t="s">
         <v>372</v>
       </c>
-      <c r="P70" s="59" t="s">
+      <c r="P70" s="43" t="s">
         <v>209</v>
       </c>
-      <c r="Q70" s="60" t="s">
+      <c r="Q70" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="R70" s="60" t="s">
+      <c r="R70" s="44" t="s">
         <v>337</v>
       </c>
-      <c r="S70" s="63" t="s">
+      <c r="S70" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V70" s="55"/>
@@ -8139,49 +8116,49 @@
     <row r="71" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B71" s="10"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q71" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R71" s="58" t="s">
+      <c r="D71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q71" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R71" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S71" s="50" t="s">
@@ -8191,52 +8168,52 @@
     </row>
     <row r="72" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B72" s="14"/>
-      <c r="D72" s="59" t="s">
+      <c r="D72" s="43" t="s">
         <v>723</v>
       </c>
-      <c r="E72" s="59" t="s">
+      <c r="E72" s="43" t="s">
         <v>632</v>
       </c>
-      <c r="F72" s="59" t="s">
+      <c r="F72" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="G72" s="59" t="s">
+      <c r="G72" s="43" t="s">
         <v>725</v>
       </c>
-      <c r="H72" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I72" s="59" t="s">
+      <c r="H72" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I72" s="43" t="s">
         <v>727</v>
       </c>
-      <c r="J72" s="59" t="s">
+      <c r="J72" s="43" t="s">
         <v>730</v>
       </c>
-      <c r="K72" s="59" t="s">
+      <c r="K72" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="L72" s="59" t="s">
+      <c r="L72" s="43" t="s">
         <v>732</v>
       </c>
-      <c r="M72" s="59" t="s">
+      <c r="M72" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="N72" s="59" t="s">
+      <c r="N72" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="O72" s="59" t="s">
+      <c r="O72" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="P72" s="59" t="s">
+      <c r="P72" s="43" t="s">
         <v>735</v>
       </c>
-      <c r="Q72" s="59" t="s">
+      <c r="Q72" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="R72" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="S72" s="62" t="s">
+      <c r="R72" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="S72" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V72" s="55"/>
@@ -8246,104 +8223,104 @@
         <f>B69+1</f>
         <v>18</v>
       </c>
-      <c r="D73" s="57" t="s">
+      <c r="D73" s="51" t="s">
         <v>556</v>
       </c>
-      <c r="E73" s="57" t="s">
+      <c r="E73" s="51" t="s">
         <v>557</v>
       </c>
-      <c r="F73" s="57" t="s">
+      <c r="F73" s="51" t="s">
         <v>236</v>
       </c>
-      <c r="G73" s="57" t="s">
+      <c r="G73" s="51" t="s">
         <v>558</v>
       </c>
-      <c r="H73" s="57" t="s">
+      <c r="H73" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="I73" s="57" t="s">
+      <c r="I73" s="51" t="s">
         <v>559</v>
       </c>
-      <c r="J73" s="57" t="s">
+      <c r="J73" s="51" t="s">
         <v>561</v>
       </c>
-      <c r="K73" s="57" t="s">
+      <c r="K73" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="L73" s="57" t="s">
+      <c r="L73" s="51" t="s">
         <v>563</v>
       </c>
-      <c r="M73" s="57" t="s">
+      <c r="M73" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="N73" s="57" t="s">
+      <c r="N73" s="51" t="s">
         <v>168</v>
       </c>
-      <c r="O73" s="57" t="s">
+      <c r="O73" s="51" t="s">
         <v>550</v>
       </c>
-      <c r="P73" s="57" t="s">
+      <c r="P73" s="51" t="s">
         <v>565</v>
       </c>
-      <c r="Q73" s="57" t="s">
+      <c r="Q73" s="51" t="s">
         <v>567</v>
       </c>
-      <c r="R73" s="57" t="s">
+      <c r="R73" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="S73" s="61" t="s">
+      <c r="S73" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V73" s="55"/>
     </row>
     <row r="74" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="16"/>
-      <c r="D74" s="59" t="s">
+      <c r="D74" s="43" t="s">
         <v>724</v>
       </c>
-      <c r="E74" s="59" t="s">
+      <c r="E74" s="43" t="s">
         <v>282</v>
       </c>
-      <c r="F74" s="59" t="s">
+      <c r="F74" s="43" t="s">
         <v>323</v>
       </c>
-      <c r="G74" s="59" t="s">
+      <c r="G74" s="43" t="s">
         <v>726</v>
       </c>
-      <c r="H74" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I74" s="59" t="s">
+      <c r="H74" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I74" s="43" t="s">
         <v>728</v>
       </c>
-      <c r="J74" s="59" t="s">
+      <c r="J74" s="43" t="s">
         <v>730</v>
       </c>
-      <c r="K74" s="59" t="s">
+      <c r="K74" s="43" t="s">
         <v>207</v>
       </c>
-      <c r="L74" s="59" t="s">
+      <c r="L74" s="43" t="s">
         <v>733</v>
       </c>
-      <c r="M74" s="59" t="s">
+      <c r="M74" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="N74" s="59" t="s">
+      <c r="N74" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="O74" s="59" t="s">
+      <c r="O74" s="43" t="s">
         <v>381</v>
       </c>
-      <c r="P74" s="59" t="s">
+      <c r="P74" s="43" t="s">
         <v>735</v>
       </c>
-      <c r="Q74" s="60" t="s">
+      <c r="Q74" s="44" t="s">
         <v>331</v>
       </c>
-      <c r="R74" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="S74" s="63" t="s">
+      <c r="R74" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="S74" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V74" s="55"/>
@@ -8351,49 +8328,49 @@
     <row r="75" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B75" s="10"/>
       <c r="C75" s="25"/>
-      <c r="D75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q75" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R75" s="58" t="s">
+      <c r="D75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q75" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R75" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S75" s="50" t="s">
@@ -8403,52 +8380,52 @@
     </row>
     <row r="76" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="14"/>
-      <c r="D76" s="59" t="s">
+      <c r="D76" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="E76" s="59" t="s">
+      <c r="E76" s="43" t="s">
         <v>652</v>
       </c>
-      <c r="F76" s="59" t="s">
+      <c r="F76" s="43" t="s">
         <v>319</v>
       </c>
-      <c r="G76" s="59" t="s">
+      <c r="G76" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="H76" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I76" s="59" t="s">
+      <c r="H76" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I76" s="43" t="s">
         <v>737</v>
       </c>
-      <c r="J76" s="59" t="s">
+      <c r="J76" s="43" t="s">
         <v>853</v>
       </c>
-      <c r="K76" s="59" t="s">
+      <c r="K76" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="L76" s="59" t="s">
+      <c r="L76" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="M76" s="59" t="s">
+      <c r="M76" s="43" t="s">
         <v>369</v>
       </c>
-      <c r="N76" s="59" t="s">
+      <c r="N76" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="O76" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="P76" s="59" t="s">
+      <c r="O76" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="P76" s="43" t="s">
         <v>707</v>
       </c>
-      <c r="Q76" s="59" t="s">
+      <c r="Q76" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="R76" s="59" t="s">
+      <c r="R76" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="S76" s="62" t="s">
+      <c r="S76" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V76" s="55"/>
@@ -8458,104 +8435,104 @@
         <f>B73+1</f>
         <v>19</v>
       </c>
-      <c r="D77" s="57" t="s">
+      <c r="D77" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="E77" s="57" t="s">
+      <c r="E77" s="51" t="s">
         <v>465</v>
       </c>
-      <c r="F77" s="57" t="s">
+      <c r="F77" s="51" t="s">
         <v>234</v>
       </c>
-      <c r="G77" s="57" t="s">
+      <c r="G77" s="51" t="s">
         <v>568</v>
       </c>
-      <c r="H77" s="57" t="s">
+      <c r="H77" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="I77" s="57" t="s">
+      <c r="I77" s="51" t="s">
         <v>570</v>
       </c>
-      <c r="J77" s="57" t="s">
+      <c r="J77" s="51" t="s">
         <v>248</v>
       </c>
-      <c r="K77" s="57" t="s">
+      <c r="K77" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="L77" s="57" t="s">
+      <c r="L77" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="M77" s="57" t="s">
+      <c r="M77" s="51" t="s">
         <v>257</v>
       </c>
-      <c r="N77" s="57" t="s">
+      <c r="N77" s="51" t="s">
         <v>572</v>
       </c>
-      <c r="O77" s="57" t="s">
+      <c r="O77" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="P77" s="57" t="s">
+      <c r="P77" s="51" t="s">
         <v>536</v>
       </c>
-      <c r="Q77" s="57" t="s">
+      <c r="Q77" s="51" t="s">
         <v>273</v>
       </c>
-      <c r="R77" s="57" t="s">
+      <c r="R77" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="S77" s="61" t="s">
+      <c r="S77" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V77" s="55"/>
     </row>
     <row r="78" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="16"/>
-      <c r="D78" s="59" t="s">
+      <c r="D78" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="E78" s="59" t="s">
+      <c r="E78" s="43" t="s">
         <v>652</v>
       </c>
-      <c r="F78" s="59" t="s">
+      <c r="F78" s="43" t="s">
         <v>320</v>
       </c>
-      <c r="G78" s="59" t="s">
+      <c r="G78" s="43" t="s">
         <v>326</v>
       </c>
-      <c r="H78" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I78" s="59" t="s">
+      <c r="H78" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I78" s="43" t="s">
         <v>738</v>
       </c>
-      <c r="J78" s="59" t="s">
+      <c r="J78" s="43" t="s">
         <v>854</v>
       </c>
-      <c r="K78" s="59" t="s">
+      <c r="K78" s="43" t="s">
         <v>401</v>
       </c>
-      <c r="L78" s="59" t="s">
+      <c r="L78" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="M78" s="59" t="s">
+      <c r="M78" s="43" t="s">
         <v>370</v>
       </c>
-      <c r="N78" s="59" t="s">
+      <c r="N78" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="O78" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="P78" s="59" t="s">
+      <c r="O78" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="P78" s="43" t="s">
         <v>708</v>
       </c>
-      <c r="Q78" s="60" t="s">
+      <c r="Q78" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="R78" s="60" t="s">
+      <c r="R78" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="S78" s="63" t="s">
+      <c r="S78" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V78" s="55"/>
@@ -8563,49 +8540,49 @@
     <row r="79" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B79" s="10"/>
       <c r="C79" s="25"/>
-      <c r="D79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q79" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R79" s="58" t="s">
+      <c r="D79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q79" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R79" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S79" s="50" t="s">
@@ -8615,52 +8592,52 @@
     </row>
     <row r="80" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="14"/>
-      <c r="D80" s="59" t="s">
+      <c r="D80" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="E80" s="59" t="s">
+      <c r="E80" s="43" t="s">
         <v>336</v>
       </c>
-      <c r="F80" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="G80" s="59" t="s">
+      <c r="F80" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G80" s="43" t="s">
         <v>702</v>
       </c>
-      <c r="H80" s="59" t="s">
+      <c r="H80" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="I80" s="59" t="s">
+      <c r="I80" s="43" t="s">
         <v>321</v>
       </c>
-      <c r="J80" s="59" t="s">
+      <c r="J80" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="K80" s="59" t="s">
+      <c r="K80" s="43" t="s">
         <v>739</v>
       </c>
-      <c r="L80" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="M80" s="59" t="s">
+      <c r="L80" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="M80" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="N80" s="59" t="s">
+      <c r="N80" s="43" t="s">
         <v>740</v>
       </c>
-      <c r="O80" s="59" t="s">
+      <c r="O80" s="43" t="s">
         <v>630</v>
       </c>
-      <c r="P80" s="59" t="s">
+      <c r="P80" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="Q80" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="R80" s="59" t="s">
+      <c r="Q80" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="R80" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="S80" s="62" t="s">
+      <c r="S80" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V80" s="55"/>
@@ -8670,104 +8647,104 @@
         <f>B77+1</f>
         <v>20</v>
       </c>
-      <c r="D81" s="57" t="s">
+      <c r="D81" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="E81" s="57" t="s">
+      <c r="E81" s="51" t="s">
         <v>554</v>
       </c>
-      <c r="F81" s="57" t="s">
+      <c r="F81" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="G81" s="57" t="s">
+      <c r="G81" s="51" t="s">
         <v>533</v>
       </c>
-      <c r="H81" s="57" t="s">
+      <c r="H81" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="I81" s="57" t="s">
+      <c r="I81" s="51" t="s">
         <v>235</v>
       </c>
-      <c r="J81" s="57" t="s">
+      <c r="J81" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="K81" s="57" t="s">
+      <c r="K81" s="51" t="s">
         <v>573</v>
       </c>
-      <c r="L81" s="57" t="s">
+      <c r="L81" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="M81" s="57" t="s">
+      <c r="M81" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="N81" s="57" t="s">
+      <c r="N81" s="51" t="s">
         <v>574</v>
       </c>
-      <c r="O81" s="57" t="s">
+      <c r="O81" s="51" t="s">
         <v>415</v>
       </c>
-      <c r="P81" s="57" t="s">
+      <c r="P81" s="51" t="s">
         <v>416</v>
       </c>
-      <c r="Q81" s="57" t="s">
+      <c r="Q81" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="R81" s="57" t="s">
+      <c r="R81" s="51" t="s">
         <v>550</v>
       </c>
-      <c r="S81" s="61" t="s">
+      <c r="S81" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V81" s="55"/>
     </row>
     <row r="82" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="16"/>
-      <c r="D82" s="59" t="s">
+      <c r="D82" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="E82" s="59" t="s">
+      <c r="E82" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="F82" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="G82" s="59" t="s">
+      <c r="F82" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G82" s="43" t="s">
         <v>703</v>
       </c>
-      <c r="H82" s="59" t="s">
+      <c r="H82" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="I82" s="59" t="s">
+      <c r="I82" s="43" t="s">
         <v>322</v>
       </c>
-      <c r="J82" s="59" t="s">
+      <c r="J82" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="K82" s="59" t="s">
+      <c r="K82" s="43" t="s">
         <v>325</v>
       </c>
-      <c r="L82" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="M82" s="59" t="s">
+      <c r="L82" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="M82" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="N82" s="59" t="s">
+      <c r="N82" s="43" t="s">
         <v>741</v>
       </c>
-      <c r="O82" s="59" t="s">
+      <c r="O82" s="43" t="s">
         <v>631</v>
       </c>
-      <c r="P82" s="59" t="s">
+      <c r="P82" s="43" t="s">
         <v>632</v>
       </c>
-      <c r="Q82" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="R82" s="60" t="s">
+      <c r="Q82" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="R82" s="44" t="s">
         <v>381</v>
       </c>
-      <c r="S82" s="63" t="s">
+      <c r="S82" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V82" s="56"/>
@@ -8775,49 +8752,49 @@
     <row r="83" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B83" s="10"/>
       <c r="C83" s="25"/>
-      <c r="D83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q83" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R83" s="58" t="s">
+      <c r="D83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q83" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R83" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S83" s="50" t="s">
@@ -8827,52 +8804,52 @@
     </row>
     <row r="84" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B84" s="14"/>
-      <c r="D84" s="59" t="s">
+      <c r="D84" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="E84" s="59" t="s">
+      <c r="E84" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="F84" s="59" t="s">
+      <c r="F84" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="G84" s="59" t="s">
+      <c r="G84" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="H84" s="59" t="s">
+      <c r="H84" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="I84" s="59" t="s">
+      <c r="I84" s="43" t="s">
         <v>377</v>
       </c>
-      <c r="J84" s="59" t="s">
+      <c r="J84" s="43" t="s">
         <v>379</v>
       </c>
-      <c r="K84" s="59" t="s">
+      <c r="K84" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="L84" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="M84" s="59" t="s">
+      <c r="L84" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="M84" s="43" t="s">
         <v>681</v>
       </c>
-      <c r="N84" s="59" t="s">
+      <c r="N84" s="43" t="s">
         <v>744</v>
       </c>
-      <c r="O84" s="59" t="s">
+      <c r="O84" s="43" t="s">
         <v>747</v>
       </c>
-      <c r="P84" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q84" s="59" t="s">
+      <c r="P84" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q84" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="R84" s="59" t="s">
+      <c r="R84" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="S84" s="62" t="s">
+      <c r="S84" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V84" s="7"/>
@@ -8882,104 +8859,104 @@
         <f>B81+1</f>
         <v>21</v>
       </c>
-      <c r="D85" s="57" t="s">
+      <c r="D85" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="E85" s="57" t="s">
+      <c r="E85" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="F85" s="57" t="s">
+      <c r="F85" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="G85" s="57" t="s">
+      <c r="G85" s="51" t="s">
         <v>431</v>
       </c>
-      <c r="H85" s="57" t="s">
+      <c r="H85" s="51" t="s">
         <v>252</v>
       </c>
-      <c r="I85" s="57" t="s">
+      <c r="I85" s="51" t="s">
         <v>276</v>
       </c>
-      <c r="J85" s="57" t="s">
+      <c r="J85" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="K85" s="57" t="s">
+      <c r="K85" s="51" t="s">
         <v>509</v>
       </c>
-      <c r="L85" s="57" t="s">
+      <c r="L85" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="M85" s="57" t="s">
+      <c r="M85" s="51" t="s">
         <v>575</v>
       </c>
-      <c r="N85" s="57" t="s">
+      <c r="N85" s="51" t="s">
         <v>577</v>
       </c>
-      <c r="O85" s="57" t="s">
+      <c r="O85" s="51" t="s">
         <v>579</v>
       </c>
-      <c r="P85" s="57" t="s">
+      <c r="P85" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="Q85" s="57" t="s">
+      <c r="Q85" s="51" t="s">
         <v>267</v>
       </c>
-      <c r="R85" s="57" t="s">
+      <c r="R85" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="S85" s="61" t="s">
+      <c r="S85" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V85" s="7"/>
     </row>
     <row r="86" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B86" s="16"/>
-      <c r="D86" s="59" t="s">
+      <c r="D86" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="E86" s="59" t="s">
+      <c r="E86" s="43" t="s">
         <v>354</v>
       </c>
-      <c r="F86" s="59" t="s">
+      <c r="F86" s="43" t="s">
         <v>354</v>
       </c>
-      <c r="G86" s="59" t="s">
+      <c r="G86" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="H86" s="59" t="s">
+      <c r="H86" s="43" t="s">
         <v>364</v>
       </c>
-      <c r="I86" s="59" t="s">
+      <c r="I86" s="43" t="s">
         <v>397</v>
       </c>
-      <c r="J86" s="59" t="s">
+      <c r="J86" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="K86" s="59" t="s">
+      <c r="K86" s="43" t="s">
         <v>307</v>
       </c>
-      <c r="L86" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="M86" s="59" t="s">
+      <c r="L86" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="M86" s="43" t="s">
         <v>742</v>
       </c>
-      <c r="N86" s="59" t="s">
+      <c r="N86" s="43" t="s">
         <v>745</v>
       </c>
-      <c r="O86" s="59" t="s">
+      <c r="O86" s="43" t="s">
         <v>748</v>
       </c>
-      <c r="P86" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q86" s="60" t="s">
+      <c r="P86" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q86" s="44" t="s">
         <v>329</v>
       </c>
-      <c r="R86" s="60" t="s">
+      <c r="R86" s="44" t="s">
         <v>287</v>
       </c>
-      <c r="S86" s="63" t="s">
+      <c r="S86" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V86" s="7"/>
@@ -8987,49 +8964,49 @@
     <row r="87" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B87" s="10"/>
       <c r="C87" s="25"/>
-      <c r="D87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q87" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R87" s="58" t="s">
+      <c r="D87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q87" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R87" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S87" s="50" t="s">
@@ -9039,52 +9016,52 @@
     </row>
     <row r="88" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B88" s="14"/>
-      <c r="D88" s="59" t="s">
+      <c r="D88" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="E88" s="59" t="s">
+      <c r="E88" s="43" t="s">
         <v>652</v>
       </c>
-      <c r="F88" s="59" t="s">
+      <c r="F88" s="43" t="s">
         <v>394</v>
       </c>
-      <c r="G88" s="59" t="s">
+      <c r="G88" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="H88" s="59" t="s">
+      <c r="H88" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="I88" s="59" t="s">
+      <c r="I88" s="43" t="s">
         <v>296</v>
       </c>
-      <c r="J88" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="K88" s="59" t="s">
+      <c r="J88" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="K88" s="43" t="s">
         <v>681</v>
       </c>
-      <c r="L88" s="59" t="s">
+      <c r="L88" s="43" t="s">
         <v>319</v>
       </c>
-      <c r="M88" s="59" t="s">
+      <c r="M88" s="43" t="s">
         <v>718</v>
       </c>
-      <c r="N88" s="59" t="s">
+      <c r="N88" s="43" t="s">
         <v>349</v>
       </c>
-      <c r="O88" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="P88" s="59" t="s">
+      <c r="O88" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="P88" s="43" t="s">
         <v>310</v>
       </c>
-      <c r="Q88" s="59" t="s">
+      <c r="Q88" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="R88" s="59" t="s">
+      <c r="R88" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="S88" s="62" t="s">
+      <c r="S88" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V88" s="7"/>
@@ -9094,104 +9071,104 @@
         <f>B85+1</f>
         <v>22</v>
       </c>
-      <c r="D89" s="57" t="s">
+      <c r="D89" s="51" t="s">
         <v>277</v>
       </c>
-      <c r="E89" s="57" t="s">
+      <c r="E89" s="51" t="s">
         <v>465</v>
       </c>
-      <c r="F89" s="57" t="s">
+      <c r="F89" s="51" t="s">
         <v>581</v>
       </c>
-      <c r="G89" s="57" t="s">
+      <c r="G89" s="51" t="s">
         <v>582</v>
       </c>
-      <c r="H89" s="57" t="s">
+      <c r="H89" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="I89" s="57" t="s">
+      <c r="I89" s="51" t="s">
         <v>231</v>
       </c>
-      <c r="J89" s="57" t="s">
+      <c r="J89" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="K89" s="57" t="s">
+      <c r="K89" s="51" t="s">
         <v>575</v>
       </c>
-      <c r="L89" s="57" t="s">
+      <c r="L89" s="51" t="s">
         <v>234</v>
       </c>
-      <c r="M89" s="57" t="s">
+      <c r="M89" s="51" t="s">
         <v>546</v>
       </c>
-      <c r="N89" s="57" t="s">
+      <c r="N89" s="51" t="s">
         <v>244</v>
       </c>
-      <c r="O89" s="57" t="s">
+      <c r="O89" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="P89" s="57" t="s">
+      <c r="P89" s="51" t="s">
         <v>584</v>
       </c>
-      <c r="Q89" s="57" t="s">
+      <c r="Q89" s="51" t="s">
         <v>256</v>
       </c>
-      <c r="R89" s="57" t="s">
+      <c r="R89" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="S89" s="61" t="s">
+      <c r="S89" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V89" s="7"/>
     </row>
     <row r="90" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B90" s="16"/>
-      <c r="D90" s="59" t="s">
+      <c r="D90" s="43" t="s">
         <v>382</v>
       </c>
-      <c r="E90" s="59" t="s">
+      <c r="E90" s="43" t="s">
         <v>652</v>
       </c>
-      <c r="F90" s="59" t="s">
+      <c r="F90" s="43" t="s">
         <v>395</v>
       </c>
-      <c r="G90" s="59" t="s">
+      <c r="G90" s="43" t="s">
         <v>380</v>
       </c>
-      <c r="H90" s="59" t="s">
+      <c r="H90" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="I90" s="59" t="s">
+      <c r="I90" s="43" t="s">
         <v>297</v>
       </c>
-      <c r="J90" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="K90" s="59" t="s">
+      <c r="J90" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="K90" s="43" t="s">
         <v>742</v>
       </c>
-      <c r="L90" s="59" t="s">
+      <c r="L90" s="43" t="s">
         <v>320</v>
       </c>
-      <c r="M90" s="59" t="s">
+      <c r="M90" s="43" t="s">
         <v>719</v>
       </c>
-      <c r="N90" s="59" t="s">
+      <c r="N90" s="43" t="s">
         <v>349</v>
       </c>
-      <c r="O90" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="P90" s="59" t="s">
+      <c r="O90" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="P90" s="43" t="s">
         <v>311</v>
       </c>
-      <c r="Q90" s="60" t="s">
+      <c r="Q90" s="44" t="s">
         <v>201</v>
       </c>
-      <c r="R90" s="60" t="s">
+      <c r="R90" s="44" t="s">
         <v>368</v>
       </c>
-      <c r="S90" s="63" t="s">
+      <c r="S90" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V90" s="7"/>
@@ -9199,49 +9176,49 @@
     <row r="91" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B91" s="10"/>
       <c r="C91" s="25"/>
-      <c r="D91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q91" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R91" s="58" t="s">
+      <c r="D91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q91" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R91" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S91" s="50" t="s">
@@ -9251,52 +9228,52 @@
     </row>
     <row r="92" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B92" s="14"/>
-      <c r="D92" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="E92" s="59" t="s">
+      <c r="D92" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="E92" s="43" t="s">
         <v>313</v>
       </c>
-      <c r="F92" s="59" t="s">
+      <c r="F92" s="43" t="s">
         <v>856</v>
       </c>
-      <c r="G92" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="H92" s="59" t="s">
+      <c r="G92" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="H92" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="I92" s="59" t="s">
+      <c r="I92" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="J92" s="59" t="s">
+      <c r="J92" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="K92" s="59" t="s">
+      <c r="K92" s="43" t="s">
         <v>353</v>
       </c>
-      <c r="L92" s="59" t="s">
+      <c r="L92" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="M92" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N92" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="O92" s="59" t="s">
+      <c r="M92" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N92" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="O92" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="P92" s="59" t="s">
+      <c r="P92" s="43" t="s">
         <v>345</v>
       </c>
-      <c r="Q92" s="59" t="s">
+      <c r="Q92" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="R92" s="59" t="s">
+      <c r="R92" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="S92" s="62" t="s">
+      <c r="S92" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V92" s="7"/>
@@ -9306,104 +9283,104 @@
         <f>B89+1</f>
         <v>23</v>
       </c>
-      <c r="D93" s="57" t="s">
+      <c r="D93" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="E93" s="57" t="s">
+      <c r="E93" s="51" t="s">
         <v>585</v>
       </c>
-      <c r="F93" s="57" t="s">
+      <c r="F93" s="51" t="s">
         <v>587</v>
       </c>
-      <c r="G93" s="57" t="s">
+      <c r="G93" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="H93" s="57" t="s">
+      <c r="H93" s="51" t="s">
         <v>550</v>
       </c>
-      <c r="I93" s="57" t="s">
+      <c r="I93" s="51" t="s">
         <v>253</v>
       </c>
-      <c r="J93" s="57" t="s">
+      <c r="J93" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="K93" s="57" t="s">
+      <c r="K93" s="51" t="s">
         <v>589</v>
       </c>
-      <c r="L93" s="57" t="s">
+      <c r="L93" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="M93" s="57" t="s">
+      <c r="M93" s="51" t="s">
         <v>417</v>
       </c>
-      <c r="N93" s="57" t="s">
+      <c r="N93" s="51" t="s">
         <v>590</v>
       </c>
-      <c r="O93" s="57" t="s">
+      <c r="O93" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="P93" s="57" t="s">
+      <c r="P93" s="51" t="s">
         <v>591</v>
       </c>
-      <c r="Q93" s="57" t="s">
+      <c r="Q93" s="51" t="s">
         <v>431</v>
       </c>
-      <c r="R93" s="57" t="s">
+      <c r="R93" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="S93" s="61" t="s">
+      <c r="S93" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V93" s="7"/>
     </row>
     <row r="94" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B94" s="16"/>
-      <c r="D94" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="E94" s="59" t="s">
+      <c r="D94" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="E94" s="43" t="s">
         <v>129</v>
       </c>
-      <c r="F94" s="59" t="s">
+      <c r="F94" s="43" t="s">
         <v>352</v>
       </c>
-      <c r="G94" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="H94" s="59" t="s">
+      <c r="G94" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="H94" s="43" t="s">
         <v>381</v>
       </c>
-      <c r="I94" s="59" t="s">
+      <c r="I94" s="43" t="s">
         <v>366</v>
       </c>
-      <c r="J94" s="59" t="s">
+      <c r="J94" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="K94" s="59" t="s">
+      <c r="K94" s="43" t="s">
         <v>750</v>
       </c>
-      <c r="L94" s="59" t="s">
+      <c r="L94" s="43" t="s">
         <v>209</v>
       </c>
-      <c r="M94" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N94" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="O94" s="59" t="s">
+      <c r="M94" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N94" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="O94" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="P94" s="59" t="s">
+      <c r="P94" s="43" t="s">
         <v>346</v>
       </c>
-      <c r="Q94" s="60" t="s">
+      <c r="Q94" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="R94" s="60" t="s">
+      <c r="R94" s="44" t="s">
         <v>401</v>
       </c>
-      <c r="S94" s="63" t="s">
+      <c r="S94" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V94" s="7"/>
@@ -9411,22 +9388,22 @@
     <row r="95" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B95" s="10"/>
       <c r="C95" s="25"/>
-      <c r="D95" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E95" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F95" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G95" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H95" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I95" s="58" t="s">
+      <c r="D95" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E95" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F95" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G95" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H95" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I95" s="41" t="s">
         <v>156</v>
       </c>
       <c r="J95" s="41" t="s">
@@ -9463,22 +9440,22 @@
     </row>
     <row r="96" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B96" s="14"/>
-      <c r="D96" s="59" t="s">
+      <c r="D96" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="E96" s="59" t="s">
+      <c r="E96" s="43" t="s">
         <v>751</v>
       </c>
-      <c r="F96" s="59" t="s">
+      <c r="F96" s="43" t="s">
         <v>753</v>
       </c>
-      <c r="G96" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="H96" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I96" s="59" t="s">
+      <c r="G96" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="H96" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I96" s="43" t="s">
         <v>156</v>
       </c>
       <c r="J96" s="43" t="s">
@@ -9518,22 +9495,22 @@
         <f>B93+1</f>
         <v>24</v>
       </c>
-      <c r="D97" s="57" t="s">
+      <c r="D97" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="E97" s="57" t="s">
+      <c r="E97" s="51" t="s">
         <v>592</v>
       </c>
-      <c r="F97" s="57" t="s">
+      <c r="F97" s="51" t="s">
         <v>593</v>
       </c>
-      <c r="G97" s="57" t="s">
+      <c r="G97" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="H97" s="57" t="s">
+      <c r="H97" s="51" t="s">
         <v>594</v>
       </c>
-      <c r="I97" s="57" t="str">
+      <c r="I97" s="51" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -9572,22 +9549,22 @@
     </row>
     <row r="98" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B98" s="16"/>
-      <c r="D98" s="59" t="s">
+      <c r="D98" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="E98" s="59" t="s">
+      <c r="E98" s="43" t="s">
         <v>752</v>
       </c>
-      <c r="F98" s="59" t="s">
+      <c r="F98" s="43" t="s">
         <v>754</v>
       </c>
-      <c r="G98" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="H98" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="I98" s="59" t="s">
+      <c r="G98" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="H98" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I98" s="43" t="s">
         <v>156</v>
       </c>
       <c r="J98" s="43" t="s">
@@ -9625,49 +9602,49 @@
     <row r="99" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B99" s="10"/>
       <c r="C99" s="25"/>
-      <c r="D99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q99" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R99" s="58" t="s">
+      <c r="D99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q99" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R99" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S99" s="50" t="s">
@@ -9677,52 +9654,52 @@
     </row>
     <row r="100" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B100" s="14"/>
-      <c r="D100" s="59" t="s">
+      <c r="D100" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="E100" s="59" t="s">
+      <c r="E100" s="43" t="s">
         <v>319</v>
       </c>
-      <c r="F100" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="G100" s="59" t="s">
+      <c r="F100" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G100" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="H100" s="59" t="s">
+      <c r="H100" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="I100" s="59" t="s">
+      <c r="I100" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="J100" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="K100" s="59" t="s">
+      <c r="J100" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="K100" s="43" t="s">
         <v>658</v>
       </c>
-      <c r="L100" s="59" t="s">
+      <c r="L100" s="43" t="s">
         <v>332</v>
       </c>
-      <c r="M100" s="59" t="s">
+      <c r="M100" s="43" t="s">
         <v>355</v>
       </c>
-      <c r="N100" s="59" t="s">
+      <c r="N100" s="43" t="s">
         <v>213</v>
       </c>
-      <c r="O100" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="P100" s="59" t="s">
+      <c r="O100" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="P100" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="Q100" s="59" t="s">
+      <c r="Q100" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="R100" s="59" t="s">
+      <c r="R100" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="S100" s="62" t="s">
+      <c r="S100" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V100" s="7"/>
@@ -9732,104 +9709,104 @@
         <f>B97+1</f>
         <v>25</v>
       </c>
-      <c r="D101" s="57" t="s">
+      <c r="D101" s="51" t="s">
         <v>275</v>
       </c>
-      <c r="E101" s="57" t="s">
+      <c r="E101" s="51" t="s">
         <v>234</v>
       </c>
-      <c r="F101" s="57" t="s">
+      <c r="F101" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="G101" s="57" t="s">
+      <c r="G101" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="H101" s="57" t="s">
+      <c r="H101" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="I101" s="57" t="s">
+      <c r="I101" s="51" t="s">
         <v>478</v>
       </c>
-      <c r="J101" s="57" t="s">
+      <c r="J101" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="K101" s="57" t="s">
+      <c r="K101" s="51" t="s">
         <v>469</v>
       </c>
-      <c r="L101" s="57" t="s">
+      <c r="L101" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="M101" s="57" t="s">
+      <c r="M101" s="51" t="s">
         <v>596</v>
       </c>
-      <c r="N101" s="57" t="s">
+      <c r="N101" s="51" t="s">
         <v>233</v>
       </c>
-      <c r="O101" s="57" t="s">
+      <c r="O101" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="P101" s="57" t="s">
+      <c r="P101" s="51" t="s">
         <v>264</v>
       </c>
-      <c r="Q101" s="57" t="s">
+      <c r="Q101" s="51" t="s">
         <v>264</v>
       </c>
-      <c r="R101" s="57" t="s">
+      <c r="R101" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="S101" s="61" t="s">
+      <c r="S101" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V101" s="7"/>
     </row>
     <row r="102" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B102" s="16"/>
-      <c r="D102" s="59" t="s">
+      <c r="D102" s="43" t="s">
         <v>392</v>
       </c>
-      <c r="E102" s="59" t="s">
+      <c r="E102" s="43" t="s">
         <v>320</v>
       </c>
-      <c r="F102" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="G102" s="59" t="s">
+      <c r="F102" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G102" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="H102" s="59" t="s">
+      <c r="H102" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="I102" s="59" t="s">
+      <c r="I102" s="43" t="s">
         <v>664</v>
       </c>
-      <c r="J102" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="K102" s="59" t="s">
+      <c r="J102" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="K102" s="43" t="s">
         <v>659</v>
       </c>
-      <c r="L102" s="59" t="s">
+      <c r="L102" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="M102" s="59" t="s">
+      <c r="M102" s="43" t="s">
         <v>289</v>
       </c>
-      <c r="N102" s="59" t="s">
+      <c r="N102" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="O102" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="P102" s="59" t="s">
+      <c r="O102" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="P102" s="43" t="s">
         <v>381</v>
       </c>
-      <c r="Q102" s="60" t="s">
+      <c r="Q102" s="44" t="s">
         <v>381</v>
       </c>
-      <c r="R102" s="60" t="s">
+      <c r="R102" s="44" t="s">
         <v>380</v>
       </c>
-      <c r="S102" s="63" t="s">
+      <c r="S102" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V102" s="7"/>
@@ -9837,49 +9814,49 @@
     <row r="103" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B103" s="10"/>
       <c r="C103" s="25"/>
-      <c r="D103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q103" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R103" s="58" t="s">
+      <c r="D103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q103" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R103" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S103" s="50" t="s">
@@ -9889,52 +9866,52 @@
     </row>
     <row r="104" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B104" s="14"/>
-      <c r="D104" s="59" t="s">
+      <c r="D104" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E104" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="F104" s="59" t="s">
+      <c r="E104" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="F104" s="43" t="s">
         <v>755</v>
       </c>
-      <c r="G104" s="59" t="s">
+      <c r="G104" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="H104" s="59" t="s">
+      <c r="H104" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="I104" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="J104" s="59" t="s">
+      <c r="I104" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="J104" s="43" t="s">
         <v>858</v>
       </c>
-      <c r="K104" s="59" t="s">
+      <c r="K104" s="43" t="s">
         <v>633</v>
       </c>
-      <c r="L104" s="59" t="s">
+      <c r="L104" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="M104" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N104" s="59" t="s">
+      <c r="M104" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N104" s="43" t="s">
         <v>758</v>
       </c>
-      <c r="O104" s="59" t="s">
+      <c r="O104" s="43" t="s">
         <v>193</v>
       </c>
-      <c r="P104" s="59" t="s">
+      <c r="P104" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="Q104" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="R104" s="59" t="s">
+      <c r="Q104" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="R104" s="43" t="s">
         <v>633</v>
       </c>
-      <c r="S104" s="62" t="s">
+      <c r="S104" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V104" s="7"/>
@@ -9944,104 +9921,104 @@
         <f>B101+1</f>
         <v>26</v>
       </c>
-      <c r="D105" s="57" t="s">
+      <c r="D105" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="E105" s="57" t="s">
+      <c r="E105" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="F105" s="57" t="s">
+      <c r="F105" s="51" t="s">
         <v>597</v>
       </c>
-      <c r="G105" s="57" t="s">
+      <c r="G105" s="51" t="s">
         <v>218</v>
       </c>
-      <c r="H105" s="57" t="s">
+      <c r="H105" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="I105" s="57" t="s">
+      <c r="I105" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="J105" s="57" t="s">
+      <c r="J105" s="51" t="s">
         <v>599</v>
       </c>
-      <c r="K105" s="57" t="s">
+      <c r="K105" s="51" t="s">
         <v>422</v>
       </c>
-      <c r="L105" s="57" t="s">
+      <c r="L105" s="51" t="s">
         <v>600</v>
       </c>
-      <c r="M105" s="57" t="s">
+      <c r="M105" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="N105" s="57" t="s">
+      <c r="N105" s="51" t="s">
         <v>602</v>
       </c>
-      <c r="O105" s="57" t="s">
+      <c r="O105" s="51" t="s">
         <v>227</v>
       </c>
-      <c r="P105" s="57" t="s">
+      <c r="P105" s="51" t="s">
         <v>550</v>
       </c>
-      <c r="Q105" s="57" t="s">
+      <c r="Q105" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="R105" s="57" t="s">
+      <c r="R105" s="51" t="s">
         <v>422</v>
       </c>
-      <c r="S105" s="61" t="s">
+      <c r="S105" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V105" s="7"/>
     </row>
     <row r="106" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B106" s="16"/>
-      <c r="D106" s="59" t="s">
+      <c r="D106" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E106" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="F106" s="59" t="s">
+      <c r="E106" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="F106" s="43" t="s">
         <v>756</v>
       </c>
-      <c r="G106" s="59" t="s">
+      <c r="G106" s="43" t="s">
         <v>279</v>
       </c>
-      <c r="H106" s="59" t="s">
+      <c r="H106" s="43" t="s">
         <v>288</v>
       </c>
-      <c r="I106" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="J106" s="59" t="s">
+      <c r="I106" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="J106" s="43" t="s">
         <v>859</v>
       </c>
-      <c r="K106" s="59" t="s">
+      <c r="K106" s="43" t="s">
         <v>294</v>
       </c>
-      <c r="L106" s="59" t="s">
+      <c r="L106" s="43" t="s">
         <v>338</v>
       </c>
-      <c r="M106" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="N106" s="59" t="s">
+      <c r="M106" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="N106" s="43" t="s">
         <v>759</v>
       </c>
-      <c r="O106" s="59" t="s">
+      <c r="O106" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="P106" s="59" t="s">
+      <c r="P106" s="43" t="s">
         <v>381</v>
       </c>
-      <c r="Q106" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="R106" s="60" t="s">
+      <c r="Q106" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="R106" s="44" t="s">
         <v>294</v>
       </c>
-      <c r="S106" s="63" t="s">
+      <c r="S106" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V106" s="7"/>
@@ -10049,49 +10026,49 @@
     <row r="107" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B107" s="10"/>
       <c r="C107" s="25"/>
-      <c r="D107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q107" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R107" s="58" t="s">
+      <c r="D107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q107" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R107" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S107" s="50" t="s">
@@ -10101,52 +10078,52 @@
     </row>
     <row r="108" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B108" s="14"/>
-      <c r="D108" s="59" t="s">
+      <c r="D108" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="E108" s="59" t="s">
+      <c r="E108" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F108" s="59" t="s">
+      <c r="F108" s="43" t="s">
         <v>693</v>
       </c>
-      <c r="G108" s="59" t="s">
+      <c r="G108" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="H108" s="59" t="s">
+      <c r="H108" s="43" t="s">
         <v>374</v>
       </c>
-      <c r="I108" s="59" t="s">
+      <c r="I108" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="J108" s="59" t="s">
+      <c r="J108" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="K108" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="L108" s="59" t="s">
+      <c r="K108" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="L108" s="43" t="s">
         <v>761</v>
       </c>
-      <c r="M108" s="59" t="s">
+      <c r="M108" s="43" t="s">
         <v>355</v>
       </c>
-      <c r="N108" s="59" t="s">
+      <c r="N108" s="43" t="s">
         <v>379</v>
       </c>
-      <c r="O108" s="59" t="s">
+      <c r="O108" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="P108" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q108" s="59" t="s">
+      <c r="P108" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q108" s="43" t="s">
         <v>737</v>
       </c>
-      <c r="R108" s="59" t="s">
+      <c r="R108" s="43" t="s">
         <v>764</v>
       </c>
-      <c r="S108" s="62" t="s">
+      <c r="S108" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V108" s="7"/>
@@ -10156,104 +10133,104 @@
         <f>B105+1</f>
         <v>27</v>
       </c>
-      <c r="D109" s="57" t="s">
+      <c r="D109" s="51" t="s">
         <v>600</v>
       </c>
-      <c r="E109" s="57" t="s">
+      <c r="E109" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="F109" s="57" t="s">
+      <c r="F109" s="51" t="s">
         <v>604</v>
       </c>
-      <c r="G109" s="57" t="s">
+      <c r="G109" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="H109" s="57" t="s">
+      <c r="H109" s="51" t="s">
         <v>606</v>
       </c>
-      <c r="I109" s="57" t="s">
+      <c r="I109" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="J109" s="57" t="s">
+      <c r="J109" s="51" t="s">
         <v>510</v>
       </c>
-      <c r="K109" s="57" t="s">
+      <c r="K109" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="L109" s="57" t="s">
+      <c r="L109" s="51" t="s">
         <v>608</v>
       </c>
-      <c r="M109" s="57" t="s">
+      <c r="M109" s="51" t="s">
         <v>596</v>
       </c>
-      <c r="N109" s="57" t="s">
+      <c r="N109" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="O109" s="57" t="s">
+      <c r="O109" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="P109" s="57" t="s">
+      <c r="P109" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="Q109" s="57" t="s">
+      <c r="Q109" s="51" t="s">
         <v>570</v>
       </c>
-      <c r="R109" s="57" t="s">
+      <c r="R109" s="51" t="s">
         <v>610</v>
       </c>
-      <c r="S109" s="61" t="s">
+      <c r="S109" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V109" s="7"/>
     </row>
     <row r="110" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B110" s="16"/>
-      <c r="D110" s="59" t="s">
+      <c r="D110" s="43" t="s">
         <v>338</v>
       </c>
-      <c r="E110" s="59" t="s">
+      <c r="E110" s="43" t="s">
         <v>183</v>
       </c>
-      <c r="F110" s="59" t="s">
+      <c r="F110" s="43" t="s">
         <v>376</v>
       </c>
-      <c r="G110" s="59" t="s">
+      <c r="G110" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="H110" s="59" t="s">
+      <c r="H110" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="I110" s="59" t="s">
+      <c r="I110" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="J110" s="59" t="s">
+      <c r="J110" s="43" t="s">
         <v>694</v>
       </c>
-      <c r="K110" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="L110" s="59" t="s">
+      <c r="K110" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="L110" s="43" t="s">
         <v>762</v>
       </c>
-      <c r="M110" s="59" t="s">
+      <c r="M110" s="43" t="s">
         <v>289</v>
       </c>
-      <c r="N110" s="59" t="s">
+      <c r="N110" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="O110" s="59" t="s">
+      <c r="O110" s="43" t="s">
         <v>380</v>
       </c>
-      <c r="P110" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q110" s="60" t="s">
+      <c r="P110" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q110" s="44" t="s">
         <v>738</v>
       </c>
-      <c r="R110" s="60" t="s">
+      <c r="R110" s="44" t="s">
         <v>765</v>
       </c>
-      <c r="S110" s="63" t="s">
+      <c r="S110" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V110" s="7"/>
@@ -10261,25 +10238,25 @@
     <row r="111" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B111" s="10"/>
       <c r="C111" s="25"/>
-      <c r="D111" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E111" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F111" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G111" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H111" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I111" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J111" s="58" t="s">
+      <c r="D111" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E111" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F111" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G111" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H111" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I111" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J111" s="41" t="s">
         <v>156</v>
       </c>
       <c r="K111" s="41" t="s">
@@ -10313,25 +10290,25 @@
     </row>
     <row r="112" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B112" s="14"/>
-      <c r="D112" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="E112" s="59" t="s">
+      <c r="D112" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="E112" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="F112" s="59" t="s">
+      <c r="F112" s="43" t="s">
         <v>652</v>
       </c>
-      <c r="G112" s="59" t="s">
+      <c r="G112" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="H112" s="59" t="s">
+      <c r="H112" s="43" t="s">
         <v>213</v>
       </c>
-      <c r="I112" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="J112" s="59" t="s">
+      <c r="I112" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="J112" s="43" t="s">
         <v>156</v>
       </c>
       <c r="K112" s="43" t="s">
@@ -10368,25 +10345,25 @@
         <f>B109+1</f>
         <v>28</v>
       </c>
-      <c r="D113" s="57" t="s">
+      <c r="D113" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="E113" s="57" t="s">
+      <c r="E113" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="F113" s="57" t="s">
+      <c r="F113" s="51" t="s">
         <v>465</v>
       </c>
-      <c r="G113" s="57" t="s">
+      <c r="G113" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="H113" s="57" t="s">
+      <c r="H113" s="51" t="s">
         <v>233</v>
       </c>
-      <c r="I113" s="57" t="s">
+      <c r="I113" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="J113" s="57" t="str">
+      <c r="J113" s="51" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -10422,25 +10399,25 @@
     </row>
     <row r="114" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B114" s="16"/>
-      <c r="D114" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="E114" s="59" t="s">
+      <c r="D114" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="E114" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="F114" s="59" t="s">
+      <c r="F114" s="43" t="s">
         <v>652</v>
       </c>
-      <c r="G114" s="59" t="s">
+      <c r="G114" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="H114" s="59" t="s">
+      <c r="H114" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="I114" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="J114" s="59" t="s">
+      <c r="I114" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="J114" s="43" t="s">
         <v>156</v>
       </c>
       <c r="K114" s="43" t="s">
@@ -10475,49 +10452,49 @@
     <row r="115" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B115" s="10"/>
       <c r="C115" s="25"/>
-      <c r="D115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q115" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R115" s="58" t="s">
+      <c r="D115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q115" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R115" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S115" s="50" t="s">
@@ -10527,52 +10504,52 @@
     </row>
     <row r="116" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B116" s="14"/>
-      <c r="D116" s="59" t="s">
+      <c r="D116" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="E116" s="59" t="s">
+      <c r="E116" s="43" t="s">
         <v>154</v>
       </c>
-      <c r="F116" s="59" t="s">
+      <c r="F116" s="43" t="s">
         <v>152</v>
       </c>
-      <c r="G116" s="59" t="s">
+      <c r="G116" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="H116" s="59" t="s">
+      <c r="H116" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="I116" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="J116" s="59" t="s">
+      <c r="I116" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="J116" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="K116" s="59" t="s">
+      <c r="K116" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="L116" s="59" t="s">
+      <c r="L116" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="M116" s="59" t="s">
+      <c r="M116" s="43" t="s">
         <v>753</v>
       </c>
-      <c r="N116" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="O116" s="59" t="s">
+      <c r="N116" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="O116" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="P116" s="59" t="s">
+      <c r="P116" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="Q116" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="R116" s="59" t="s">
+      <c r="Q116" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="R116" s="43" t="s">
         <v>767</v>
       </c>
-      <c r="S116" s="62" t="s">
+      <c r="S116" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V116" s="7"/>
@@ -10582,104 +10559,104 @@
         <f>B113+1</f>
         <v>29</v>
       </c>
-      <c r="D117" s="57" t="s">
+      <c r="D117" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="E117" s="57" t="s">
+      <c r="E117" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="F117" s="57" t="s">
+      <c r="F117" s="51" t="s">
         <v>611</v>
       </c>
-      <c r="G117" s="57" t="s">
+      <c r="G117" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="H117" s="57" t="s">
+      <c r="H117" s="51" t="s">
         <v>613</v>
       </c>
-      <c r="I117" s="57" t="s">
+      <c r="I117" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="J117" s="57" t="s">
+      <c r="J117" s="51" t="s">
         <v>162</v>
       </c>
-      <c r="K117" s="57" t="s">
+      <c r="K117" s="51" t="s">
         <v>614</v>
       </c>
-      <c r="L117" s="57" t="s">
+      <c r="L117" s="51" t="s">
         <v>229</v>
       </c>
-      <c r="M117" s="57" t="s">
+      <c r="M117" s="51" t="s">
         <v>593</v>
       </c>
-      <c r="N117" s="57" t="s">
+      <c r="N117" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="O117" s="57" t="s">
+      <c r="O117" s="51" t="s">
         <v>509</v>
       </c>
-      <c r="P117" s="57" t="s">
+      <c r="P117" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="Q117" s="57" t="s">
+      <c r="Q117" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="R117" s="57" t="s">
+      <c r="R117" s="51" t="s">
         <v>616</v>
       </c>
-      <c r="S117" s="61" t="s">
+      <c r="S117" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V117" s="7"/>
     </row>
     <row r="118" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B118" s="16"/>
-      <c r="D118" s="59" t="s">
+      <c r="D118" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="E118" s="59" t="s">
+      <c r="E118" s="43" t="s">
         <v>155</v>
       </c>
-      <c r="F118" s="59" t="s">
+      <c r="F118" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="G118" s="59" t="s">
+      <c r="G118" s="43" t="s">
         <v>207</v>
       </c>
-      <c r="H118" s="59" t="s">
+      <c r="H118" s="43" t="s">
         <v>392</v>
       </c>
-      <c r="I118" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="J118" s="59" t="s">
+      <c r="I118" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="J118" s="43" t="s">
         <v>181</v>
       </c>
-      <c r="K118" s="59" t="s">
+      <c r="K118" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="L118" s="59" t="s">
+      <c r="L118" s="43" t="s">
         <v>312</v>
       </c>
-      <c r="M118" s="59" t="s">
+      <c r="M118" s="43" t="s">
         <v>754</v>
       </c>
-      <c r="N118" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="O118" s="59" t="s">
+      <c r="N118" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="O118" s="43" t="s">
         <v>307</v>
       </c>
-      <c r="P118" s="59" t="s">
+      <c r="P118" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="Q118" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="R118" s="60" t="s">
+      <c r="Q118" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="R118" s="44" t="s">
         <v>767</v>
       </c>
-      <c r="S118" s="63" t="s">
+      <c r="S118" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V118" s="7"/>
@@ -10687,49 +10664,49 @@
     <row r="119" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B119" s="10"/>
       <c r="C119" s="25"/>
-      <c r="D119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="H119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="I119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="J119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="K119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="L119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="M119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="N119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="O119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="P119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q119" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="R119" s="58" t="s">
+      <c r="D119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="H119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="I119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="J119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="K119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="L119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="M119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="N119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="O119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="P119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q119" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R119" s="41" t="s">
         <v>156</v>
       </c>
       <c r="S119" s="50" t="s">
@@ -10739,52 +10716,52 @@
     </row>
     <row r="120" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B120" s="14"/>
-      <c r="D120" s="59" t="s">
+      <c r="D120" s="43" t="s">
         <v>677</v>
       </c>
-      <c r="E120" s="59" t="s">
+      <c r="E120" s="43" t="s">
         <v>768</v>
       </c>
-      <c r="F120" s="59" t="s">
+      <c r="F120" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="G120" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="H120" s="59" t="s">
+      <c r="G120" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="H120" s="43" t="s">
         <v>770</v>
       </c>
-      <c r="I120" s="59" t="s">
+      <c r="I120" s="43" t="s">
         <v>773</v>
       </c>
-      <c r="J120" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="K120" s="59" t="s">
+      <c r="J120" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="K120" s="43" t="s">
         <v>761</v>
       </c>
-      <c r="L120" s="59" t="s">
+      <c r="L120" s="43" t="s">
         <v>775</v>
       </c>
-      <c r="M120" s="59" t="s">
+      <c r="M120" s="43" t="s">
         <v>348</v>
       </c>
-      <c r="N120" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="O120" s="59" t="s">
+      <c r="N120" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="O120" s="43" t="s">
         <v>777</v>
       </c>
-      <c r="P120" s="59" t="s">
+      <c r="P120" s="43" t="s">
         <v>737</v>
       </c>
-      <c r="Q120" s="59" t="s">
+      <c r="Q120" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="R120" s="59" t="s">
+      <c r="R120" s="43" t="s">
         <v>707</v>
       </c>
-      <c r="S120" s="62" t="s">
+      <c r="S120" s="46" t="s">
         <v>156</v>
       </c>
       <c r="V120" s="7"/>
@@ -10794,104 +10771,104 @@
         <f>B117+1</f>
         <v>30</v>
       </c>
-      <c r="D121" s="57" t="s">
+      <c r="D121" s="51" t="s">
         <v>489</v>
       </c>
-      <c r="E121" s="57" t="s">
+      <c r="E121" s="51" t="s">
         <v>618</v>
       </c>
-      <c r="F121" s="57" t="s">
+      <c r="F121" s="51" t="s">
         <v>510</v>
       </c>
-      <c r="G121" s="57" t="s">
+      <c r="G121" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="H121" s="57" t="s">
+      <c r="H121" s="51" t="s">
         <v>619</v>
       </c>
-      <c r="I121" s="57" t="s">
+      <c r="I121" s="51" t="s">
         <v>621</v>
       </c>
-      <c r="J121" s="57" t="s">
+      <c r="J121" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="K121" s="57" t="s">
+      <c r="K121" s="51" t="s">
         <v>608</v>
       </c>
-      <c r="L121" s="57" t="s">
+      <c r="L121" s="51" t="s">
         <v>622</v>
       </c>
-      <c r="M121" s="57" t="s">
+      <c r="M121" s="51" t="s">
         <v>268</v>
       </c>
-      <c r="N121" s="57" t="s">
+      <c r="N121" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="O121" s="57" t="s">
+      <c r="O121" s="51" t="s">
         <v>623</v>
       </c>
-      <c r="P121" s="57" t="s">
+      <c r="P121" s="51" t="s">
         <v>570</v>
       </c>
-      <c r="Q121" s="57" t="s">
+      <c r="Q121" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="R121" s="57" t="s">
+      <c r="R121" s="51" t="s">
         <v>536</v>
       </c>
-      <c r="S121" s="61" t="s">
+      <c r="S121" s="45" t="s">
         <v>156</v>
       </c>
       <c r="V121" s="7"/>
     </row>
     <row r="122" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B122" s="16"/>
-      <c r="D122" s="59" t="s">
+      <c r="D122" s="43" t="s">
         <v>678</v>
       </c>
-      <c r="E122" s="59" t="s">
+      <c r="E122" s="43" t="s">
         <v>769</v>
       </c>
-      <c r="F122" s="59" t="s">
+      <c r="F122" s="43" t="s">
         <v>694</v>
       </c>
-      <c r="G122" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="H122" s="59" t="s">
+      <c r="G122" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="H122" s="43" t="s">
         <v>771</v>
       </c>
-      <c r="I122" s="59" t="s">
+      <c r="I122" s="43" t="s">
         <v>774</v>
       </c>
-      <c r="J122" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="K122" s="59" t="s">
+      <c r="J122" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="K122" s="43" t="s">
         <v>762</v>
       </c>
-      <c r="L122" s="59" t="s">
+      <c r="L122" s="43" t="s">
         <v>776</v>
       </c>
-      <c r="M122" s="59" t="s">
+      <c r="M122" s="43" t="s">
         <v>348</v>
       </c>
-      <c r="N122" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="O122" s="59" t="s">
+      <c r="N122" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="O122" s="43" t="s">
         <v>778</v>
       </c>
-      <c r="P122" s="59" t="s">
+      <c r="P122" s="43" t="s">
         <v>738</v>
       </c>
-      <c r="Q122" s="60" t="s">
+      <c r="Q122" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="R122" s="60" t="s">
+      <c r="R122" s="44" t="s">
         <v>708</v>
       </c>
-      <c r="S122" s="63" t="s">
+      <c r="S122" s="49" t="s">
         <v>156</v>
       </c>
       <c r="V122" s="7"/>
@@ -10899,16 +10876,16 @@
     <row r="123" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B123" s="10"/>
       <c r="C123" s="25"/>
-      <c r="D123" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E123" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="F123" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="G123" s="58" t="s">
+      <c r="D123" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="E123" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="F123" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="G123" s="41" t="s">
         <v>156</v>
       </c>
       <c r="H123" s="41" t="s">
@@ -10951,16 +10928,16 @@
     </row>
     <row r="124" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B124" s="14"/>
-      <c r="D124" s="59" t="s">
+      <c r="D124" s="43" t="s">
         <v>350</v>
       </c>
-      <c r="E124" s="59" t="s">
+      <c r="E124" s="43" t="s">
         <v>779</v>
       </c>
-      <c r="F124" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="G124" s="59" t="s">
+      <c r="F124" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G124" s="43" t="s">
         <v>156</v>
       </c>
       <c r="H124" s="43" t="s">
@@ -11006,16 +10983,16 @@
         <f>B121+1</f>
         <v>31</v>
       </c>
-      <c r="D125" s="57" t="s">
+      <c r="D125" s="51" t="s">
         <v>245</v>
       </c>
-      <c r="E125" s="57" t="s">
+      <c r="E125" s="51" t="s">
         <v>624</v>
       </c>
-      <c r="F125" s="57" t="s">
+      <c r="F125" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="G125" s="57" t="str">
+      <c r="G125" s="51" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -11060,16 +11037,16 @@
     </row>
     <row r="126" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B126" s="16"/>
-      <c r="D126" s="59" t="s">
+      <c r="D126" s="43" t="s">
         <v>351</v>
       </c>
-      <c r="E126" s="59" t="s">
+      <c r="E126" s="43" t="s">
         <v>780</v>
       </c>
-      <c r="F126" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="G126" s="59" t="s">
+      <c r="F126" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G126" s="43" t="s">
         <v>156</v>
       </c>
       <c r="H126" s="43" t="s">
@@ -11113,7 +11090,7 @@
     <row r="127" spans="2:22" s="26" customFormat="1" ht="60" customHeight="1">
       <c r="B127" s="10"/>
       <c r="C127" s="25"/>
-      <c r="D127" s="58" t="s">
+      <c r="D127" s="41" t="s">
         <v>156</v>
       </c>
       <c r="E127" s="41" t="s">
@@ -11165,7 +11142,7 @@
     </row>
     <row r="128" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B128" s="14"/>
-      <c r="D128" s="59" t="s">
+      <c r="D128" s="43" t="s">
         <v>156</v>
       </c>
       <c r="E128" s="43" t="s">
@@ -11220,7 +11197,7 @@
         <f>B125+1</f>
         <v>32</v>
       </c>
-      <c r="D129" s="57" t="s">
+      <c r="D129" s="51" t="s">
         <v>177</v>
       </c>
       <c r="E129" s="51" t="s">
@@ -11272,7 +11249,7 @@
     </row>
     <row r="130" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B130" s="16"/>
-      <c r="D130" s="59" t="s">
+      <c r="D130" s="43" t="s">
         <v>156</v>
       </c>
       <c r="E130" s="43" t="s">

--- a/output7/【河洛文讀注音-閩拼調號】《桃花源記》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調號】《桃花源記》.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A92F070-540A-4910-9C6E-45C84F6C2A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0586AB1-C72E-47B5-BBB2-C9DBCEC66841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" tabRatio="718" activeTab="1" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="28680" yWindow="-195" windowWidth="38640" windowHeight="15720" tabRatio="718" activeTab="1" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -866,9 +866,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>閩拼調符</t>
-  </si>
-  <si>
     <t>郡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3254,6 +3251,9 @@
   <si>
     <t>gge5</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白話字</t>
   </si>
 </sst>
 </file>
@@ -4205,7 +4205,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -4213,7 +4213,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="7" spans="2:11">
@@ -4221,7 +4221,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D7" s="36"/>
       <c r="E7" s="36"/>
@@ -4317,7 +4317,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>217</v>
+        <v>859</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="30">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="T3" s="13"/>
       <c r="V3" s="54" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
@@ -4537,13 +4537,13 @@
         <v>156</v>
       </c>
       <c r="E4" s="43" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F4" s="43" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H4" s="43" t="s">
         <v>49</v>
@@ -4558,7 +4558,7 @@
         <v>156</v>
       </c>
       <c r="L4" s="43" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="M4" s="43" t="s">
         <v>86</v>
@@ -4567,7 +4567,7 @@
         <v>156</v>
       </c>
       <c r="O4" s="43" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="P4" s="43" t="s">
         <v>75</v>
@@ -4591,16 +4591,16 @@
         <v>157</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F5" s="51" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G5" s="51" t="s">
+        <v>412</v>
+      </c>
+      <c r="H5" s="51" t="s">
         <v>413</v>
-      </c>
-      <c r="H5" s="51" t="s">
-        <v>414</v>
       </c>
       <c r="I5" s="51" t="s">
         <v>158</v>
@@ -4612,22 +4612,22 @@
         <v>159</v>
       </c>
       <c r="L5" s="51" t="s">
+        <v>414</v>
+      </c>
+      <c r="M5" s="51" t="s">
         <v>415</v>
       </c>
-      <c r="M5" s="51" t="s">
+      <c r="N5" s="51" t="s">
         <v>416</v>
       </c>
-      <c r="N5" s="51" t="s">
-        <v>417</v>
-      </c>
       <c r="O5" s="51" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P5" s="51" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Q5" s="51" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="R5" s="51" t="str">
         <f>CHAR(10)</f>
@@ -4646,16 +4646,16 @@
         <v>156</v>
       </c>
       <c r="E6" s="43" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F6" s="43" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H6" s="43" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I6" s="43" t="s">
         <v>156</v>
@@ -4667,22 +4667,22 @@
         <v>156</v>
       </c>
       <c r="L6" s="43" t="s">
+        <v>630</v>
+      </c>
+      <c r="M6" s="43" t="s">
         <v>631</v>
       </c>
-      <c r="M6" s="43" t="s">
-        <v>632</v>
-      </c>
       <c r="N6" s="43" t="s">
         <v>156</v>
       </c>
       <c r="O6" s="43" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P6" s="43" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q6" s="44" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R6" s="44" t="s">
         <v>156</v>
@@ -4738,7 +4738,7 @@
         <v>156</v>
       </c>
       <c r="R7" s="41" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="S7" s="48" t="s">
         <v>156</v>
@@ -4751,10 +4751,10 @@
         <v>86</v>
       </c>
       <c r="E8" s="43" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F8" s="43" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G8" s="43" t="s">
         <v>130</v>
@@ -4763,7 +4763,7 @@
         <v>156</v>
       </c>
       <c r="I8" s="43" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J8" s="43" t="s">
         <v>36</v>
@@ -4772,7 +4772,7 @@
         <v>39</v>
       </c>
       <c r="L8" s="43" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="M8" s="43" t="s">
         <v>76</v>
@@ -4781,16 +4781,16 @@
         <v>82</v>
       </c>
       <c r="O8" s="43" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P8" s="43" t="s">
         <v>156</v>
       </c>
       <c r="Q8" s="43" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="R8" s="43" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="S8" s="46" t="s">
         <v>156</v>
@@ -4803,49 +4803,49 @@
         <v>2</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H9" s="51" t="s">
         <v>163</v>
       </c>
       <c r="I9" s="51" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J9" s="51" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="K9" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L9" s="51" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M9" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="N9" s="51" t="s">
         <v>430</v>
       </c>
-      <c r="N9" s="51" t="s">
-        <v>431</v>
-      </c>
       <c r="O9" s="51" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P9" s="51" t="s">
         <v>165</v>
       </c>
       <c r="Q9" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R9" s="51" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="S9" s="45" t="s">
         <v>156</v>
@@ -4856,49 +4856,49 @@
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="16"/>
       <c r="D10" s="43" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H10" s="43" t="s">
         <v>156</v>
       </c>
       <c r="I10" s="43" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J10" s="43" t="s">
         <v>188</v>
       </c>
       <c r="K10" s="43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L10" s="43" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="M10" s="43" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N10" s="43" t="s">
         <v>189</v>
       </c>
       <c r="O10" s="43" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P10" s="43" t="s">
         <v>156</v>
       </c>
       <c r="Q10" s="44" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="R10" s="44" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="S10" s="49" t="s">
         <v>156</v>
@@ -4979,22 +4979,22 @@
         <v>52</v>
       </c>
       <c r="J12" s="43" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="K12" s="43" t="s">
         <v>156</v>
       </c>
       <c r="L12" s="43" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="M12" s="43" t="s">
         <v>191</v>
       </c>
       <c r="N12" s="43" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="O12" s="43" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="P12" s="43" t="s">
         <v>81</v>
@@ -5003,7 +5003,7 @@
         <v>156</v>
       </c>
       <c r="R12" s="43" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="S12" s="46" t="s">
         <v>156</v>
@@ -5016,49 +5016,49 @@
         <v>3</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E13" s="51" t="s">
         <v>163</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H13" s="51" t="s">
         <v>171</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K13" s="51" t="s">
         <v>165</v>
       </c>
       <c r="L13" s="51" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M13" s="51" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N13" s="51" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O13" s="51" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P13" s="51" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Q13" s="51" t="s">
         <v>163</v>
       </c>
       <c r="R13" s="51" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="S13" s="45" t="s">
         <v>156</v>
@@ -5074,7 +5074,7 @@
         <v>156</v>
       </c>
       <c r="F14" s="43" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G14" s="43" t="s">
         <v>214</v>
@@ -5083,34 +5083,34 @@
         <v>50</v>
       </c>
       <c r="I14" s="43" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J14" s="43" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K14" s="43" t="s">
         <v>156</v>
       </c>
       <c r="L14" s="43" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="M14" s="43" t="s">
         <v>192</v>
       </c>
       <c r="N14" s="43" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O14" s="43" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="P14" s="43" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q14" s="44" t="s">
         <v>156</v>
       </c>
       <c r="R14" s="44" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="S14" s="49" t="s">
         <v>156</v>
@@ -5182,7 +5182,7 @@
         <v>41</v>
       </c>
       <c r="G16" s="43" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H16" s="43" t="s">
         <v>156</v>
@@ -5194,7 +5194,7 @@
         <v>55</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L16" s="43" t="s">
         <v>127</v>
@@ -5206,13 +5206,13 @@
         <v>64</v>
       </c>
       <c r="O16" s="43" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="P16" s="43" t="s">
         <v>88</v>
       </c>
       <c r="Q16" s="43" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="R16" s="43" t="s">
         <v>156</v>
@@ -5228,46 +5228,46 @@
         <v>4</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H17" s="51" t="s">
         <v>163</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J17" s="51" t="s">
         <v>169</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L17" s="51" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="M17" s="51" t="s">
         <v>163</v>
       </c>
       <c r="N17" s="51" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O17" s="51" t="s">
+        <v>452</v>
+      </c>
+      <c r="P17" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="P17" s="51" t="s">
-        <v>454</v>
-      </c>
       <c r="Q17" s="51" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R17" s="51" t="s">
         <v>163</v>
@@ -5280,31 +5280,31 @@
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="16"/>
       <c r="D18" s="43" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E18" s="43" t="s">
         <v>201</v>
       </c>
       <c r="F18" s="43" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H18" s="43" t="s">
         <v>156</v>
       </c>
       <c r="I18" s="43" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J18" s="43" t="s">
         <v>197</v>
       </c>
       <c r="K18" s="43" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="L18" s="43" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M18" s="43" t="s">
         <v>156</v>
@@ -5313,13 +5313,13 @@
         <v>64</v>
       </c>
       <c r="O18" s="43" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="P18" s="43" t="s">
         <v>88</v>
       </c>
       <c r="Q18" s="44" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R18" s="44" t="s">
         <v>156</v>
@@ -5388,13 +5388,13 @@
         <v>134</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F20" s="43" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H20" s="43" t="s">
         <v>156</v>
@@ -5406,10 +5406,10 @@
         <v>39</v>
       </c>
       <c r="K20" s="43" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="L20" s="43" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="M20" s="43" t="s">
         <v>50</v>
@@ -5418,10 +5418,10 @@
         <v>156</v>
       </c>
       <c r="O20" s="43" t="s">
+        <v>651</v>
+      </c>
+      <c r="P20" s="43" t="s">
         <v>652</v>
-      </c>
-      <c r="P20" s="43" t="s">
-        <v>653</v>
       </c>
       <c r="Q20" s="43" t="s">
         <v>54</v>
@@ -5440,31 +5440,31 @@
         <v>5</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H21" s="51" t="s">
         <v>163</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="L21" s="51" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M21" s="51" t="s">
         <v>171</v>
@@ -5473,13 +5473,13 @@
         <v>165</v>
       </c>
       <c r="O21" s="51" t="s">
+        <v>464</v>
+      </c>
+      <c r="P21" s="51" t="s">
         <v>465</v>
       </c>
-      <c r="P21" s="51" t="s">
-        <v>466</v>
-      </c>
       <c r="Q21" s="51" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="R21" s="51" t="s">
         <v>163</v>
@@ -5495,28 +5495,28 @@
         <v>134</v>
       </c>
       <c r="E22" s="43" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F22" s="43" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G22" s="43" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H22" s="43" t="s">
         <v>156</v>
       </c>
       <c r="I22" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="J22" s="43" t="s">
         <v>286</v>
       </c>
-      <c r="J22" s="43" t="s">
-        <v>287</v>
-      </c>
       <c r="K22" s="43" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="L22" s="43" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="M22" s="43" t="s">
         <v>50</v>
@@ -5525,10 +5525,10 @@
         <v>156</v>
       </c>
       <c r="O22" s="43" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="P22" s="43" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="Q22" s="44" t="s">
         <v>206</v>
@@ -5597,10 +5597,10 @@
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="14"/>
       <c r="D24" s="43" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F24" s="43" t="s">
         <v>42</v>
@@ -5652,16 +5652,16 @@
         <v>6</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H25" s="51" t="s">
         <v>165</v>
@@ -5706,16 +5706,16 @@
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="16"/>
       <c r="D26" s="43" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F26" s="43" t="s">
         <v>149</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H26" s="43" t="s">
         <v>156</v>
@@ -5818,19 +5818,19 @@
         <v>81</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F28" s="43" t="s">
         <v>184</v>
       </c>
       <c r="G28" s="43" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H28" s="43" t="s">
         <v>156</v>
       </c>
       <c r="I28" s="43" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="J28" s="43" t="s">
         <v>34</v>
@@ -5851,10 +5851,10 @@
         <v>67</v>
       </c>
       <c r="P28" s="43" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="Q28" s="43" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="R28" s="43" t="s">
         <v>156</v>
@@ -5874,28 +5874,28 @@
         <v>7</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F29" s="51" t="s">
         <v>166</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H29" s="51" t="s">
         <v>163</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J29" s="51" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L29" s="51" t="s">
         <v>160</v>
@@ -5910,10 +5910,10 @@
         <v>164</v>
       </c>
       <c r="P29" s="51" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q29" s="51" t="s">
         <v>470</v>
-      </c>
-      <c r="Q29" s="51" t="s">
-        <v>471</v>
       </c>
       <c r="R29" s="51" t="s">
         <v>163</v>
@@ -5930,28 +5930,28 @@
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="16"/>
       <c r="D30" s="43" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E30" s="43" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F30" s="43" t="s">
         <v>185</v>
       </c>
       <c r="G30" s="43" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H30" s="43" t="s">
         <v>156</v>
       </c>
       <c r="I30" s="43" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="J30" s="43" t="s">
         <v>190</v>
       </c>
       <c r="K30" s="43" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L30" s="43" t="s">
         <v>53</v>
@@ -5966,10 +5966,10 @@
         <v>182</v>
       </c>
       <c r="P30" s="43" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="Q30" s="44" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="R30" s="44" t="s">
         <v>156</v>
@@ -6046,7 +6046,7 @@
         <v>192</v>
       </c>
       <c r="E32" s="43" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F32" s="43" t="s">
         <v>62</v>
@@ -6061,31 +6061,31 @@
         <v>156</v>
       </c>
       <c r="J32" s="43" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K32" s="43" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L32" s="43" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M32" s="43" t="s">
         <v>156</v>
       </c>
       <c r="N32" s="43" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="O32" s="43" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P32" s="43" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="Q32" s="43" t="s">
         <v>156</v>
       </c>
       <c r="R32" s="43" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="S32" s="46" t="s">
         <v>156</v>
@@ -6102,49 +6102,49 @@
         <v>8</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E33" s="51" t="s">
+        <v>474</v>
+      </c>
+      <c r="F33" s="51" t="s">
         <v>475</v>
-      </c>
-      <c r="F33" s="51" t="s">
-        <v>476</v>
       </c>
       <c r="G33" s="51" t="s">
         <v>164</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I33" s="51" t="s">
         <v>165</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L33" s="51" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="M33" s="51" t="s">
         <v>163</v>
       </c>
       <c r="N33" s="51" t="s">
+        <v>478</v>
+      </c>
+      <c r="O33" s="51" t="s">
+        <v>470</v>
+      </c>
+      <c r="P33" s="51" t="s">
         <v>479</v>
-      </c>
-      <c r="O33" s="51" t="s">
-        <v>471</v>
-      </c>
-      <c r="P33" s="51" t="s">
-        <v>480</v>
       </c>
       <c r="Q33" s="51" t="s">
         <v>165</v>
       </c>
       <c r="R33" s="51" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S33" s="45" t="s">
         <v>156</v>
@@ -6154,49 +6154,49 @@
     <row r="34" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="16"/>
       <c r="D34" s="43" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E34" s="43" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F34" s="43" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G34" s="43" t="s">
         <v>182</v>
       </c>
       <c r="H34" s="43" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I34" s="43" t="s">
         <v>156</v>
       </c>
       <c r="J34" s="43" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K34" s="43" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L34" s="43" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="M34" s="43" t="s">
         <v>156</v>
       </c>
       <c r="N34" s="43" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="O34" s="43" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P34" s="43" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="Q34" s="44" t="s">
         <v>156</v>
       </c>
       <c r="R34" s="44" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="S34" s="49" t="s">
         <v>156</v>
@@ -6262,16 +6262,16 @@
         <v>60</v>
       </c>
       <c r="E36" s="43" t="s">
+        <v>671</v>
+      </c>
+      <c r="F36" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G36" s="43" t="s">
+        <v>395</v>
+      </c>
+      <c r="H36" s="43" t="s">
         <v>672</v>
-      </c>
-      <c r="F36" s="43" t="s">
-        <v>156</v>
-      </c>
-      <c r="G36" s="43" t="s">
-        <v>396</v>
-      </c>
-      <c r="H36" s="43" t="s">
-        <v>673</v>
       </c>
       <c r="I36" s="43" t="s">
         <v>39</v>
@@ -6280,7 +6280,7 @@
         <v>156</v>
       </c>
       <c r="K36" s="43" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="L36" s="43" t="s">
         <v>54</v>
@@ -6289,19 +6289,19 @@
         <v>200</v>
       </c>
       <c r="N36" s="43" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O36" s="43" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="P36" s="43" t="s">
         <v>156</v>
       </c>
       <c r="Q36" s="43" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="R36" s="43" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="S36" s="46" t="s">
         <v>156</v>
@@ -6314,49 +6314,49 @@
         <v>9</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F37" s="51" t="s">
         <v>163</v>
       </c>
       <c r="G37" s="51" t="s">
+        <v>484</v>
+      </c>
+      <c r="H37" s="51" t="s">
         <v>485</v>
       </c>
-      <c r="H37" s="51" t="s">
-        <v>486</v>
-      </c>
       <c r="I37" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J37" s="51" t="s">
         <v>165</v>
       </c>
       <c r="K37" s="51" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L37" s="51" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M37" s="51" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N37" s="51" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O37" s="51" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P37" s="51" t="s">
         <v>163</v>
       </c>
       <c r="Q37" s="51" t="s">
+        <v>487</v>
+      </c>
+      <c r="R37" s="51" t="s">
         <v>488</v>
-      </c>
-      <c r="R37" s="51" t="s">
-        <v>489</v>
       </c>
       <c r="S37" s="45" t="s">
         <v>156</v>
@@ -6366,28 +6366,28 @@
     <row r="38" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="16"/>
       <c r="D38" s="43" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E38" s="43" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F38" s="43" t="s">
         <v>156</v>
       </c>
       <c r="G38" s="43" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H38" s="43" t="s">
         <v>131</v>
       </c>
       <c r="I38" s="43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J38" s="43" t="s">
         <v>156</v>
       </c>
       <c r="K38" s="43" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="L38" s="43" t="s">
         <v>206</v>
@@ -6396,19 +6396,19 @@
         <v>201</v>
       </c>
       <c r="N38" s="43" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O38" s="43" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="P38" s="43" t="s">
         <v>156</v>
       </c>
       <c r="Q38" s="44" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="R38" s="44" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="S38" s="49" t="s">
         <v>156</v>
@@ -6471,22 +6471,22 @@
     <row r="40" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="14"/>
       <c r="D40" s="43" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E40" s="43" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F40" s="43" t="s">
         <v>156</v>
       </c>
       <c r="G40" s="43" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H40" s="43" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I40" s="43" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J40" s="43" t="s">
         <v>77</v>
@@ -6495,16 +6495,16 @@
         <v>156</v>
       </c>
       <c r="L40" s="43" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="M40" s="43" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N40" s="43" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O40" s="43" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="P40" s="43" t="s">
         <v>156</v>
@@ -6526,40 +6526,40 @@
         <v>10</v>
       </c>
       <c r="D41" s="51" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F41" s="51" t="s">
         <v>165</v>
       </c>
       <c r="G41" s="51" t="s">
+        <v>493</v>
+      </c>
+      <c r="H41" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="I41" s="51" t="s">
         <v>494</v>
       </c>
-      <c r="H41" s="51" t="s">
-        <v>219</v>
-      </c>
-      <c r="I41" s="51" t="s">
-        <v>495</v>
-      </c>
       <c r="J41" s="51" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K41" s="51" t="s">
         <v>163</v>
       </c>
       <c r="L41" s="51" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M41" s="51" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N41" s="51" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O41" s="51" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="P41" s="51" t="s">
         <v>163</v>
@@ -6568,7 +6568,7 @@
         <v>164</v>
       </c>
       <c r="R41" s="51" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="S41" s="45" t="s">
         <v>156</v>
@@ -6578,40 +6578,40 @@
     <row r="42" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="16"/>
       <c r="D42" s="43" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E42" s="43" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F42" s="43" t="s">
         <v>156</v>
       </c>
       <c r="G42" s="43" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H42" s="43" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I42" s="43" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J42" s="43" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K42" s="43" t="s">
         <v>156</v>
       </c>
       <c r="L42" s="43" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="M42" s="43" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="N42" s="43" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O42" s="43" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P42" s="43" t="s">
         <v>156</v>
@@ -6683,16 +6683,16 @@
     <row r="44" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="14"/>
       <c r="D44" s="43" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E44" s="43" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F44" s="43" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G44" s="43" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H44" s="43" t="s">
         <v>203</v>
@@ -6713,19 +6713,19 @@
         <v>198</v>
       </c>
       <c r="N44" s="43" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O44" s="43" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="P44" s="43" t="s">
         <v>156</v>
       </c>
       <c r="Q44" s="43" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="R44" s="43" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="S44" s="46" t="s">
         <v>156</v>
@@ -6738,16 +6738,16 @@
         <v>11</v>
       </c>
       <c r="D45" s="51" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F45" s="51" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H45" s="51" t="s">
         <v>170</v>
@@ -6756,31 +6756,31 @@
         <v>171</v>
       </c>
       <c r="J45" s="51" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K45" s="51" t="s">
         <v>165</v>
       </c>
       <c r="L45" s="51" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="M45" s="51" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="N45" s="51" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O45" s="51" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="P45" s="51" t="s">
         <v>163</v>
       </c>
       <c r="Q45" s="51" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="R45" s="51" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="S45" s="45" t="s">
         <v>156</v>
@@ -6790,16 +6790,16 @@
     <row r="46" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="16"/>
       <c r="D46" s="43" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E46" s="43" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F46" s="43" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G46" s="43" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H46" s="43" t="s">
         <v>204</v>
@@ -6817,10 +6817,10 @@
         <v>56</v>
       </c>
       <c r="M46" s="43" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N46" s="43" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O46" s="43" t="s">
         <v>131</v>
@@ -6829,10 +6829,10 @@
         <v>156</v>
       </c>
       <c r="Q46" s="44" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="R46" s="44" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="S46" s="49" t="s">
         <v>156</v>
@@ -6895,7 +6895,7 @@
     <row r="48" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B48" s="14"/>
       <c r="D48" s="43" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E48" s="43" t="s">
         <v>48</v>
@@ -6916,7 +6916,7 @@
         <v>195</v>
       </c>
       <c r="K48" s="43" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="L48" s="43" t="s">
         <v>47</v>
@@ -6928,13 +6928,13 @@
         <v>59</v>
       </c>
       <c r="O48" s="43" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P48" s="43" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="Q48" s="43" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="R48" s="43" t="s">
         <v>156</v>
@@ -6950,46 +6950,46 @@
         <v>12</v>
       </c>
       <c r="D49" s="51" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F49" s="51" t="s">
         <v>165</v>
       </c>
       <c r="G49" s="51" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H49" s="51" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I49" s="51" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="J49" s="51" t="s">
         <v>168</v>
       </c>
       <c r="K49" s="51" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="L49" s="51" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M49" s="51" t="s">
         <v>163</v>
       </c>
       <c r="N49" s="51" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="O49" s="51" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="P49" s="51" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q49" s="51" t="s">
         <v>518</v>
-      </c>
-      <c r="Q49" s="51" t="s">
-        <v>519</v>
       </c>
       <c r="R49" s="51" t="s">
         <v>163</v>
@@ -7002,10 +7002,10 @@
     <row r="50" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="16"/>
       <c r="D50" s="43" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E50" s="43" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F50" s="43" t="s">
         <v>156</v>
@@ -7014,19 +7014,19 @@
         <v>149</v>
       </c>
       <c r="H50" s="43" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I50" s="43" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="J50" s="43" t="s">
         <v>196</v>
       </c>
       <c r="K50" s="43" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="L50" s="43" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M50" s="43" t="s">
         <v>156</v>
@@ -7035,13 +7035,13 @@
         <v>61</v>
       </c>
       <c r="O50" s="43" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="P50" s="43" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="Q50" s="44" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="R50" s="44" t="s">
         <v>156</v>
@@ -7125,28 +7125,28 @@
         <v>191</v>
       </c>
       <c r="J52" s="43" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K52" s="43" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L52" s="43" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M52" s="43" t="s">
         <v>156</v>
       </c>
       <c r="N52" s="43" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O52" s="43" t="s">
         <v>79</v>
       </c>
       <c r="P52" s="43" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Q52" s="43" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="R52" s="43" t="s">
         <v>134</v>
@@ -7162,49 +7162,49 @@
         <v>13</v>
       </c>
       <c r="D53" s="51" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F53" s="51" t="s">
         <v>132</v>
       </c>
       <c r="G53" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H53" s="51" t="s">
         <v>165</v>
       </c>
       <c r="I53" s="51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J53" s="51" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K53" s="51" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L53" s="51" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M53" s="51" t="s">
         <v>163</v>
       </c>
       <c r="N53" s="51" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="O53" s="51" t="s">
+        <v>530</v>
+      </c>
+      <c r="P53" s="51" t="s">
+        <v>488</v>
+      </c>
+      <c r="Q53" s="51" t="s">
+        <v>273</v>
+      </c>
+      <c r="R53" s="51" t="s">
         <v>531</v>
-      </c>
-      <c r="P53" s="51" t="s">
-        <v>489</v>
-      </c>
-      <c r="Q53" s="51" t="s">
-        <v>274</v>
-      </c>
-      <c r="R53" s="51" t="s">
-        <v>532</v>
       </c>
       <c r="S53" s="45" t="s">
         <v>156</v>
@@ -7220,10 +7220,10 @@
         <v>194</v>
       </c>
       <c r="F54" s="43" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G54" s="43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H54" s="43" t="s">
         <v>156</v>
@@ -7232,13 +7232,13 @@
         <v>192</v>
       </c>
       <c r="J54" s="43" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K54" s="43" t="s">
         <v>184</v>
       </c>
       <c r="L54" s="43" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M54" s="43" t="s">
         <v>156</v>
@@ -7247,13 +7247,13 @@
         <v>38</v>
       </c>
       <c r="O54" s="43" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P54" s="43" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="Q54" s="44" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R54" s="44" t="s">
         <v>134</v>
@@ -7533,7 +7533,7 @@
     <row r="60" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="14"/>
       <c r="D60" s="43" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E60" s="43" t="s">
         <v>76</v>
@@ -7545,10 +7545,10 @@
         <v>156</v>
       </c>
       <c r="H60" s="43" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="I60" s="43" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="J60" s="43" t="s">
         <v>71</v>
@@ -7557,13 +7557,13 @@
         <v>156</v>
       </c>
       <c r="L60" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="M60" s="43" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N60" s="43" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="O60" s="43" t="s">
         <v>195</v>
@@ -7575,7 +7575,7 @@
         <v>43</v>
       </c>
       <c r="R60" s="43" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="S60" s="46" t="s">
         <v>156</v>
@@ -7588,37 +7588,37 @@
         <v>15</v>
       </c>
       <c r="D61" s="51" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E61" s="51" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F61" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G61" s="51" t="s">
         <v>163</v>
       </c>
       <c r="H61" s="51" t="s">
+        <v>532</v>
+      </c>
+      <c r="I61" s="51" t="s">
         <v>533</v>
       </c>
-      <c r="I61" s="51" t="s">
-        <v>534</v>
-      </c>
       <c r="J61" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K61" s="51" t="s">
         <v>163</v>
       </c>
       <c r="L61" s="51" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="M61" s="51" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N61" s="51" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="O61" s="51" t="s">
         <v>168</v>
@@ -7627,10 +7627,10 @@
         <v>165</v>
       </c>
       <c r="Q61" s="51" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="R61" s="51" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="S61" s="45" t="s">
         <v>156</v>
@@ -7640,22 +7640,22 @@
     <row r="62" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="16"/>
       <c r="D62" s="43" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E62" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="F62" s="43" t="s">
         <v>286</v>
       </c>
-      <c r="F62" s="43" t="s">
-        <v>287</v>
-      </c>
       <c r="G62" s="43" t="s">
         <v>156</v>
       </c>
       <c r="H62" s="43" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="I62" s="43" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="J62" s="43" t="s">
         <v>216</v>
@@ -7664,13 +7664,13 @@
         <v>156</v>
       </c>
       <c r="L62" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="M62" s="43" t="s">
         <v>200</v>
       </c>
       <c r="N62" s="43" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="O62" s="43" t="s">
         <v>196</v>
@@ -7679,10 +7679,10 @@
         <v>156</v>
       </c>
       <c r="Q62" s="44" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="R62" s="44" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="S62" s="49" t="s">
         <v>156</v>
@@ -7751,43 +7751,43 @@
         <v>156</v>
       </c>
       <c r="F64" s="43" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G64" s="43" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H64" s="43" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I64" s="43" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J64" s="43" t="s">
         <v>156</v>
       </c>
       <c r="K64" s="43" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="L64" s="43" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="M64" s="43" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N64" s="43" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="O64" s="43" t="s">
         <v>47</v>
       </c>
       <c r="P64" s="43" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q64" s="43" t="s">
         <v>156</v>
       </c>
       <c r="R64" s="43" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S64" s="46" t="s">
         <v>156</v>
@@ -7806,43 +7806,43 @@
         <v>165</v>
       </c>
       <c r="F65" s="51" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G65" s="51" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H65" s="51" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I65" s="51" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J65" s="51" t="s">
         <v>163</v>
       </c>
       <c r="K65" s="51" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L65" s="51" t="s">
+        <v>545</v>
+      </c>
+      <c r="M65" s="51" t="s">
         <v>546</v>
       </c>
-      <c r="M65" s="51" t="s">
-        <v>547</v>
-      </c>
       <c r="N65" s="51" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="O65" s="51" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P65" s="51" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q65" s="51" t="s">
         <v>165</v>
       </c>
       <c r="R65" s="51" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="S65" s="45" t="s">
         <v>156</v>
@@ -7858,43 +7858,43 @@
         <v>156</v>
       </c>
       <c r="F66" s="43" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G66" s="43" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H66" s="43" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="I66" s="43" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J66" s="43" t="s">
         <v>156</v>
       </c>
       <c r="K66" s="43" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="L66" s="43" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="M66" s="43" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N66" s="43" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="O66" s="43" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P66" s="43" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q66" s="44" t="s">
         <v>156</v>
       </c>
       <c r="R66" s="44" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="S66" s="49" t="s">
         <v>156</v>
@@ -7975,22 +7975,22 @@
         <v>156</v>
       </c>
       <c r="J68" s="43" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="K68" s="43" t="s">
         <v>195</v>
       </c>
       <c r="L68" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="M68" s="43" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N68" s="43" t="s">
         <v>156</v>
       </c>
       <c r="O68" s="43" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="P68" s="43" t="s">
         <v>208</v>
@@ -7999,7 +7999,7 @@
         <v>88</v>
       </c>
       <c r="R68" s="43" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="S68" s="46" t="s">
         <v>156</v>
@@ -8012,49 +8012,49 @@
         <v>17</v>
       </c>
       <c r="D69" s="51" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E69" s="51" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F69" s="51" t="s">
         <v>164</v>
       </c>
       <c r="G69" s="51" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H69" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I69" s="51" t="s">
         <v>163</v>
       </c>
       <c r="J69" s="51" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="K69" s="51" t="s">
         <v>168</v>
       </c>
       <c r="L69" s="51" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="M69" s="51" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="N69" s="51" t="s">
         <v>165</v>
       </c>
       <c r="O69" s="51" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P69" s="51" t="s">
         <v>135</v>
       </c>
       <c r="Q69" s="51" t="s">
+        <v>552</v>
+      </c>
+      <c r="R69" s="51" t="s">
         <v>553</v>
-      </c>
-      <c r="R69" s="51" t="s">
-        <v>554</v>
       </c>
       <c r="S69" s="45" t="s">
         <v>156</v>
@@ -8064,31 +8064,31 @@
     <row r="70" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="16"/>
       <c r="D70" s="43" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E70" s="43" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F70" s="43" t="s">
         <v>182</v>
       </c>
       <c r="G70" s="43" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H70" s="43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I70" s="43" t="s">
         <v>156</v>
       </c>
       <c r="J70" s="43" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K70" s="43" t="s">
         <v>196</v>
       </c>
       <c r="L70" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="M70" s="43" t="s">
         <v>78</v>
@@ -8097,7 +8097,7 @@
         <v>156</v>
       </c>
       <c r="O70" s="43" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="P70" s="43" t="s">
         <v>209</v>
@@ -8106,7 +8106,7 @@
         <v>88</v>
       </c>
       <c r="R70" s="44" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="S70" s="49" t="s">
         <v>156</v>
@@ -8169,31 +8169,31 @@
     <row r="72" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B72" s="14"/>
       <c r="D72" s="43" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E72" s="43" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F72" s="43" t="s">
         <v>87</v>
       </c>
       <c r="G72" s="43" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H72" s="43" t="s">
         <v>156</v>
       </c>
       <c r="I72" s="43" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="J72" s="43" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K72" s="43" t="s">
         <v>33</v>
       </c>
       <c r="L72" s="43" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="M72" s="43" t="s">
         <v>39</v>
@@ -8205,7 +8205,7 @@
         <v>57</v>
       </c>
       <c r="P72" s="43" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="Q72" s="43" t="s">
         <v>70</v>
@@ -8224,46 +8224,46 @@
         <v>18</v>
       </c>
       <c r="D73" s="51" t="s">
+        <v>555</v>
+      </c>
+      <c r="E73" s="51" t="s">
         <v>556</v>
       </c>
-      <c r="E73" s="51" t="s">
+      <c r="F73" s="51" t="s">
+        <v>235</v>
+      </c>
+      <c r="G73" s="51" t="s">
         <v>557</v>
-      </c>
-      <c r="F73" s="51" t="s">
-        <v>236</v>
-      </c>
-      <c r="G73" s="51" t="s">
-        <v>558</v>
       </c>
       <c r="H73" s="51" t="s">
         <v>163</v>
       </c>
       <c r="I73" s="51" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J73" s="51" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K73" s="51" t="s">
         <v>174</v>
       </c>
       <c r="L73" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M73" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N73" s="51" t="s">
         <v>168</v>
       </c>
       <c r="O73" s="51" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="P73" s="51" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Q73" s="51" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="R73" s="51" t="s">
         <v>163</v>
@@ -8276,46 +8276,46 @@
     <row r="74" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="16"/>
       <c r="D74" s="43" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E74" s="43" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F74" s="43" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G74" s="43" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H74" s="43" t="s">
         <v>156</v>
       </c>
       <c r="I74" s="43" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="J74" s="43" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K74" s="43" t="s">
         <v>207</v>
       </c>
       <c r="L74" s="43" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="M74" s="43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N74" s="43" t="s">
         <v>196</v>
       </c>
       <c r="O74" s="43" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P74" s="43" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="Q74" s="44" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R74" s="44" t="s">
         <v>156</v>
@@ -8384,10 +8384,10 @@
         <v>63</v>
       </c>
       <c r="E76" s="43" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F76" s="43" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G76" s="43" t="s">
         <v>75</v>
@@ -8396,10 +8396,10 @@
         <v>156</v>
       </c>
       <c r="I76" s="43" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J76" s="43" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="K76" s="43" t="s">
         <v>133</v>
@@ -8408,7 +8408,7 @@
         <v>39</v>
       </c>
       <c r="M76" s="43" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N76" s="43" t="s">
         <v>143</v>
@@ -8417,7 +8417,7 @@
         <v>156</v>
       </c>
       <c r="P76" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q76" s="43" t="s">
         <v>44</v>
@@ -8439,43 +8439,43 @@
         <v>161</v>
       </c>
       <c r="E77" s="51" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F77" s="51" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G77" s="51" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H77" s="51" t="s">
         <v>163</v>
       </c>
       <c r="I77" s="51" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J77" s="51" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K77" s="51" t="s">
         <v>132</v>
       </c>
       <c r="L77" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M77" s="51" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N77" s="51" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="O77" s="51" t="s">
         <v>165</v>
       </c>
       <c r="P77" s="51" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="Q77" s="51" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R77" s="51" t="s">
         <v>167</v>
@@ -8491,31 +8491,31 @@
         <v>180</v>
       </c>
       <c r="E78" s="43" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F78" s="43" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G78" s="43" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H78" s="43" t="s">
         <v>156</v>
       </c>
       <c r="I78" s="43" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="J78" s="43" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="K78" s="43" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L78" s="43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M78" s="43" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N78" s="43" t="s">
         <v>144</v>
@@ -8524,7 +8524,7 @@
         <v>156</v>
       </c>
       <c r="P78" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="Q78" s="44" t="s">
         <v>202</v>
@@ -8596,25 +8596,25 @@
         <v>40</v>
       </c>
       <c r="E80" s="43" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F80" s="43" t="s">
         <v>156</v>
       </c>
       <c r="G80" s="43" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H80" s="43" t="s">
         <v>63</v>
       </c>
       <c r="I80" s="43" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J80" s="43" t="s">
         <v>67</v>
       </c>
       <c r="K80" s="43" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="L80" s="43" t="s">
         <v>156</v>
@@ -8623,10 +8623,10 @@
         <v>55</v>
       </c>
       <c r="N80" s="43" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="O80" s="43" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="P80" s="43" t="s">
         <v>86</v>
@@ -8651,25 +8651,25 @@
         <v>176</v>
       </c>
       <c r="E81" s="51" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F81" s="51" t="s">
         <v>163</v>
       </c>
       <c r="G81" s="51" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H81" s="51" t="s">
         <v>161</v>
       </c>
       <c r="I81" s="51" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J81" s="51" t="s">
         <v>164</v>
       </c>
       <c r="K81" s="51" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L81" s="51" t="s">
         <v>163</v>
@@ -8678,19 +8678,19 @@
         <v>169</v>
       </c>
       <c r="N81" s="51" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="O81" s="51" t="s">
+        <v>414</v>
+      </c>
+      <c r="P81" s="51" t="s">
         <v>415</v>
-      </c>
-      <c r="P81" s="51" t="s">
-        <v>416</v>
       </c>
       <c r="Q81" s="51" t="s">
         <v>165</v>
       </c>
       <c r="R81" s="51" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="S81" s="45" t="s">
         <v>156</v>
@@ -8703,25 +8703,25 @@
         <v>210</v>
       </c>
       <c r="E82" s="43" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F82" s="43" t="s">
         <v>156</v>
       </c>
       <c r="G82" s="43" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H82" s="43" t="s">
         <v>180</v>
       </c>
       <c r="I82" s="43" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J82" s="43" t="s">
         <v>182</v>
       </c>
       <c r="K82" s="43" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L82" s="43" t="s">
         <v>156</v>
@@ -8730,19 +8730,19 @@
         <v>197</v>
       </c>
       <c r="N82" s="43" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O82" s="43" t="s">
+        <v>630</v>
+      </c>
+      <c r="P82" s="43" t="s">
         <v>631</v>
       </c>
-      <c r="P82" s="43" t="s">
-        <v>632</v>
-      </c>
       <c r="Q82" s="44" t="s">
         <v>156</v>
       </c>
       <c r="R82" s="44" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="S82" s="49" t="s">
         <v>156</v>
@@ -8820,10 +8820,10 @@
         <v>43</v>
       </c>
       <c r="I84" s="43" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J84" s="43" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K84" s="43" t="s">
         <v>48</v>
@@ -8832,13 +8832,13 @@
         <v>156</v>
       </c>
       <c r="M84" s="43" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="N84" s="43" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="O84" s="43" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="P84" s="43" t="s">
         <v>156</v>
@@ -8860,49 +8860,49 @@
         <v>21</v>
       </c>
       <c r="D85" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E85" s="51" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F85" s="51" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G85" s="51" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H85" s="51" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I85" s="51" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J85" s="51" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K85" s="51" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L85" s="51" t="s">
         <v>163</v>
       </c>
       <c r="M85" s="51" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="N85" s="51" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="O85" s="51" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="P85" s="51" t="s">
         <v>165</v>
       </c>
       <c r="Q85" s="51" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R85" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S85" s="45" t="s">
         <v>156</v>
@@ -8912,49 +8912,49 @@
     <row r="86" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B86" s="16"/>
       <c r="D86" s="43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E86" s="43" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F86" s="43" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G86" s="43" t="s">
         <v>189</v>
       </c>
       <c r="H86" s="43" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I86" s="43" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J86" s="43" t="s">
         <v>200</v>
       </c>
       <c r="K86" s="43" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L86" s="43" t="s">
         <v>156</v>
       </c>
       <c r="M86" s="43" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="N86" s="43" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="O86" s="43" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="P86" s="43" t="s">
         <v>156</v>
       </c>
       <c r="Q86" s="44" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="R86" s="44" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="S86" s="49" t="s">
         <v>156</v>
@@ -9020,10 +9020,10 @@
         <v>68</v>
       </c>
       <c r="E88" s="43" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F88" s="43" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G88" s="43" t="s">
         <v>69</v>
@@ -9032,28 +9032,28 @@
         <v>42</v>
       </c>
       <c r="I88" s="43" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J88" s="43" t="s">
         <v>156</v>
       </c>
       <c r="K88" s="43" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L88" s="43" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M88" s="43" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="N88" s="43" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O88" s="43" t="s">
         <v>156</v>
       </c>
       <c r="P88" s="43" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q88" s="43" t="s">
         <v>200</v>
@@ -9072,49 +9072,49 @@
         <v>22</v>
       </c>
       <c r="D89" s="51" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E89" s="51" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F89" s="51" t="s">
+        <v>580</v>
+      </c>
+      <c r="G89" s="51" t="s">
         <v>581</v>
       </c>
-      <c r="G89" s="51" t="s">
-        <v>582</v>
-      </c>
       <c r="H89" s="51" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I89" s="51" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J89" s="51" t="s">
         <v>163</v>
       </c>
       <c r="K89" s="51" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L89" s="51" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M89" s="51" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="N89" s="51" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O89" s="51" t="s">
         <v>165</v>
       </c>
       <c r="P89" s="51" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="Q89" s="51" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R89" s="51" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="S89" s="45" t="s">
         <v>156</v>
@@ -9124,49 +9124,49 @@
     <row r="90" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B90" s="16"/>
       <c r="D90" s="43" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E90" s="43" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F90" s="43" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G90" s="43" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H90" s="43" t="s">
         <v>149</v>
       </c>
       <c r="I90" s="43" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J90" s="43" t="s">
         <v>156</v>
       </c>
       <c r="K90" s="43" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="L90" s="43" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M90" s="43" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="N90" s="43" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O90" s="43" t="s">
         <v>156</v>
       </c>
       <c r="P90" s="43" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q90" s="44" t="s">
         <v>201</v>
       </c>
       <c r="R90" s="44" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="S90" s="49" t="s">
         <v>156</v>
@@ -9232,10 +9232,10 @@
         <v>156</v>
       </c>
       <c r="E92" s="43" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F92" s="43" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G92" s="43" t="s">
         <v>156</v>
@@ -9250,7 +9250,7 @@
         <v>39</v>
       </c>
       <c r="K92" s="43" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L92" s="43" t="s">
         <v>208</v>
@@ -9265,7 +9265,7 @@
         <v>63</v>
       </c>
       <c r="P92" s="43" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q92" s="43" t="s">
         <v>82</v>
@@ -9287,43 +9287,43 @@
         <v>163</v>
       </c>
       <c r="E93" s="51" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F93" s="51" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G93" s="51" t="s">
         <v>165</v>
       </c>
       <c r="H93" s="51" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I93" s="51" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J93" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K93" s="51" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="L93" s="51" t="s">
         <v>175</v>
       </c>
       <c r="M93" s="51" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N93" s="51" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="O93" s="51" t="s">
         <v>161</v>
       </c>
       <c r="P93" s="51" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="Q93" s="51" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="R93" s="51" t="s">
         <v>132</v>
@@ -9342,22 +9342,22 @@
         <v>129</v>
       </c>
       <c r="F94" s="43" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G94" s="43" t="s">
         <v>156</v>
       </c>
       <c r="H94" s="43" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I94" s="43" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J94" s="43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K94" s="43" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="L94" s="43" t="s">
         <v>209</v>
@@ -9372,13 +9372,13 @@
         <v>180</v>
       </c>
       <c r="P94" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q94" s="44" t="s">
         <v>189</v>
       </c>
       <c r="R94" s="44" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="S94" s="49" t="s">
         <v>156</v>
@@ -9444,10 +9444,10 @@
         <v>39</v>
       </c>
       <c r="E96" s="43" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F96" s="43" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="G96" s="43" t="s">
         <v>156</v>
@@ -9496,19 +9496,19 @@
         <v>24</v>
       </c>
       <c r="D97" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E97" s="51" t="s">
+        <v>591</v>
+      </c>
+      <c r="F97" s="51" t="s">
         <v>592</v>
-      </c>
-      <c r="F97" s="51" t="s">
-        <v>593</v>
       </c>
       <c r="G97" s="51" t="s">
         <v>165</v>
       </c>
       <c r="H97" s="51" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="I97" s="51" t="str">
         <f>CHAR(10)</f>
@@ -9550,13 +9550,13 @@
     <row r="98" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B98" s="16"/>
       <c r="D98" s="43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E98" s="43" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F98" s="43" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G98" s="43" t="s">
         <v>156</v>
@@ -9658,7 +9658,7 @@
         <v>49</v>
       </c>
       <c r="E100" s="43" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F100" s="43" t="s">
         <v>156</v>
@@ -9670,19 +9670,19 @@
         <v>42</v>
       </c>
       <c r="I100" s="43" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J100" s="43" t="s">
         <v>156</v>
       </c>
       <c r="K100" s="43" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="L100" s="43" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M100" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N100" s="43" t="s">
         <v>213</v>
@@ -9710,49 +9710,49 @@
         <v>25</v>
       </c>
       <c r="D101" s="51" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E101" s="51" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F101" s="51" t="s">
         <v>163</v>
       </c>
       <c r="G101" s="51" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H101" s="51" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I101" s="51" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J101" s="51" t="s">
         <v>163</v>
       </c>
       <c r="K101" s="51" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L101" s="51" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M101" s="51" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N101" s="51" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="O101" s="51" t="s">
         <v>163</v>
       </c>
       <c r="P101" s="51" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q101" s="51" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="R101" s="51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="S101" s="45" t="s">
         <v>156</v>
@@ -9762,10 +9762,10 @@
     <row r="102" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B102" s="16"/>
       <c r="D102" s="43" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E102" s="43" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F102" s="43" t="s">
         <v>156</v>
@@ -9777,19 +9777,19 @@
         <v>149</v>
       </c>
       <c r="I102" s="43" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J102" s="43" t="s">
         <v>156</v>
       </c>
       <c r="K102" s="43" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="L102" s="43" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M102" s="43" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N102" s="43" t="s">
         <v>214</v>
@@ -9798,13 +9798,13 @@
         <v>156</v>
       </c>
       <c r="P102" s="43" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q102" s="44" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R102" s="44" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="S102" s="49" t="s">
         <v>156</v>
@@ -9873,7 +9873,7 @@
         <v>156</v>
       </c>
       <c r="F104" s="43" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G104" s="43" t="s">
         <v>37</v>
@@ -9885,10 +9885,10 @@
         <v>156</v>
       </c>
       <c r="J104" s="43" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K104" s="43" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="L104" s="43" t="s">
         <v>35</v>
@@ -9897,7 +9897,7 @@
         <v>156</v>
       </c>
       <c r="N104" s="43" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="O104" s="43" t="s">
         <v>193</v>
@@ -9909,7 +9909,7 @@
         <v>156</v>
       </c>
       <c r="R104" s="43" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="S104" s="46" t="s">
         <v>156</v>
@@ -9928,43 +9928,43 @@
         <v>165</v>
       </c>
       <c r="F105" s="51" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G105" s="51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H105" s="51" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I105" s="51" t="s">
         <v>163</v>
       </c>
       <c r="J105" s="51" t="s">
+        <v>598</v>
+      </c>
+      <c r="K105" s="51" t="s">
+        <v>421</v>
+      </c>
+      <c r="L105" s="51" t="s">
         <v>599</v>
-      </c>
-      <c r="K105" s="51" t="s">
-        <v>422</v>
-      </c>
-      <c r="L105" s="51" t="s">
-        <v>600</v>
       </c>
       <c r="M105" s="51" t="s">
         <v>163</v>
       </c>
       <c r="N105" s="51" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="O105" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P105" s="51" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q105" s="51" t="s">
         <v>165</v>
       </c>
       <c r="R105" s="51" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="S105" s="45" t="s">
         <v>156</v>
@@ -9980,43 +9980,43 @@
         <v>156</v>
       </c>
       <c r="F106" s="43" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G106" s="43" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H106" s="43" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I106" s="43" t="s">
         <v>156</v>
       </c>
       <c r="J106" s="43" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="K106" s="43" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L106" s="43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M106" s="43" t="s">
         <v>156</v>
       </c>
       <c r="N106" s="43" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="O106" s="43" t="s">
         <v>194</v>
       </c>
       <c r="P106" s="43" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q106" s="44" t="s">
         <v>156</v>
       </c>
       <c r="R106" s="44" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="S106" s="49" t="s">
         <v>156</v>
@@ -10085,13 +10085,13 @@
         <v>58</v>
       </c>
       <c r="F108" s="43" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G108" s="43" t="s">
         <v>39</v>
       </c>
       <c r="H108" s="43" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I108" s="43" t="s">
         <v>42</v>
@@ -10103,13 +10103,13 @@
         <v>156</v>
       </c>
       <c r="L108" s="43" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="M108" s="43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N108" s="43" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O108" s="43" t="s">
         <v>69</v>
@@ -10118,10 +10118,10 @@
         <v>156</v>
       </c>
       <c r="Q108" s="43" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="R108" s="43" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="S108" s="46" t="s">
         <v>156</v>
@@ -10134,49 +10134,49 @@
         <v>27</v>
       </c>
       <c r="D109" s="51" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E109" s="51" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F109" s="51" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G109" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H109" s="51" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I109" s="51" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J109" s="51" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K109" s="51" t="s">
         <v>163</v>
       </c>
       <c r="L109" s="51" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="M109" s="51" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N109" s="51" t="s">
+        <v>261</v>
+      </c>
+      <c r="O109" s="51" t="s">
         <v>262</v>
-      </c>
-      <c r="O109" s="51" t="s">
-        <v>263</v>
       </c>
       <c r="P109" s="51" t="s">
         <v>163</v>
       </c>
       <c r="Q109" s="51" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="R109" s="51" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="S109" s="45" t="s">
         <v>156</v>
@@ -10186,16 +10186,16 @@
     <row r="110" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B110" s="16"/>
       <c r="D110" s="43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E110" s="43" t="s">
         <v>183</v>
       </c>
       <c r="F110" s="43" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G110" s="43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H110" s="43" t="s">
         <v>184</v>
@@ -10204,31 +10204,31 @@
         <v>149</v>
       </c>
       <c r="J110" s="43" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="K110" s="43" t="s">
         <v>156</v>
       </c>
       <c r="L110" s="43" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="M110" s="43" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N110" s="43" t="s">
         <v>200</v>
       </c>
       <c r="O110" s="43" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P110" s="43" t="s">
         <v>156</v>
       </c>
       <c r="Q110" s="44" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="R110" s="44" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="S110" s="49" t="s">
         <v>156</v>
@@ -10297,7 +10297,7 @@
         <v>63</v>
       </c>
       <c r="F112" s="43" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G112" s="43" t="s">
         <v>34</v>
@@ -10352,13 +10352,13 @@
         <v>161</v>
       </c>
       <c r="F113" s="51" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G113" s="51" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H113" s="51" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I113" s="51" t="s">
         <v>165</v>
@@ -10406,7 +10406,7 @@
         <v>180</v>
       </c>
       <c r="F114" s="43" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G114" s="43" t="s">
         <v>190</v>
@@ -10532,7 +10532,7 @@
         <v>127</v>
       </c>
       <c r="M116" s="43" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="N116" s="43" t="s">
         <v>156</v>
@@ -10547,7 +10547,7 @@
         <v>156</v>
       </c>
       <c r="R116" s="43" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="S116" s="46" t="s">
         <v>156</v>
@@ -10566,13 +10566,13 @@
         <v>173</v>
       </c>
       <c r="F117" s="51" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G117" s="51" t="s">
         <v>174</v>
       </c>
       <c r="H117" s="51" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="I117" s="51" t="s">
         <v>163</v>
@@ -10581,19 +10581,19 @@
         <v>162</v>
       </c>
       <c r="K117" s="51" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L117" s="51" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M117" s="51" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="N117" s="51" t="s">
         <v>163</v>
       </c>
       <c r="O117" s="51" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="P117" s="51" t="s">
         <v>171</v>
@@ -10602,7 +10602,7 @@
         <v>163</v>
       </c>
       <c r="R117" s="51" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="S117" s="45" t="s">
         <v>156</v>
@@ -10624,7 +10624,7 @@
         <v>207</v>
       </c>
       <c r="H118" s="43" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I118" s="43" t="s">
         <v>156</v>
@@ -10636,16 +10636,16 @@
         <v>151</v>
       </c>
       <c r="L118" s="43" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M118" s="43" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="N118" s="43" t="s">
         <v>156</v>
       </c>
       <c r="O118" s="43" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P118" s="43" t="s">
         <v>50</v>
@@ -10654,7 +10654,7 @@
         <v>156</v>
       </c>
       <c r="R118" s="44" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="S118" s="49" t="s">
         <v>156</v>
@@ -10717,10 +10717,10 @@
     <row r="120" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B120" s="14"/>
       <c r="D120" s="43" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E120" s="43" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F120" s="43" t="s">
         <v>215</v>
@@ -10729,37 +10729,37 @@
         <v>156</v>
       </c>
       <c r="H120" s="43" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I120" s="43" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="J120" s="43" t="s">
         <v>156</v>
       </c>
       <c r="K120" s="43" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L120" s="43" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="M120" s="43" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="N120" s="43" t="s">
         <v>156</v>
       </c>
       <c r="O120" s="43" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="P120" s="43" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="Q120" s="43" t="s">
         <v>55</v>
       </c>
       <c r="R120" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="S120" s="46" t="s">
         <v>156</v>
@@ -10772,49 +10772,49 @@
         <v>30</v>
       </c>
       <c r="D121" s="51" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E121" s="51" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F121" s="51" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G121" s="51" t="s">
         <v>165</v>
       </c>
       <c r="H121" s="51" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I121" s="51" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="J121" s="51" t="s">
         <v>163</v>
       </c>
       <c r="K121" s="51" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="L121" s="51" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="M121" s="51" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N121" s="51" t="s">
         <v>163</v>
       </c>
       <c r="O121" s="51" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="P121" s="51" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="Q121" s="51" t="s">
         <v>169</v>
       </c>
       <c r="R121" s="51" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="S121" s="45" t="s">
         <v>156</v>
@@ -10824,49 +10824,49 @@
     <row r="122" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B122" s="16"/>
       <c r="D122" s="43" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E122" s="43" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F122" s="43" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G122" s="43" t="s">
         <v>156</v>
       </c>
       <c r="H122" s="43" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="I122" s="43" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="J122" s="43" t="s">
         <v>156</v>
       </c>
       <c r="K122" s="43" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="L122" s="43" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="M122" s="43" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="N122" s="43" t="s">
         <v>156</v>
       </c>
       <c r="O122" s="43" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="P122" s="43" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="Q122" s="44" t="s">
         <v>197</v>
       </c>
       <c r="R122" s="44" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="S122" s="49" t="s">
         <v>156</v>
@@ -10929,10 +10929,10 @@
     <row r="124" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B124" s="14"/>
       <c r="D124" s="43" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E124" s="43" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F124" s="43" t="s">
         <v>156</v>
@@ -10984,10 +10984,10 @@
         <v>31</v>
       </c>
       <c r="D125" s="51" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E125" s="51" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F125" s="51" t="s">
         <v>165</v>
@@ -11038,10 +11038,10 @@
     <row r="126" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B126" s="16"/>
       <c r="D126" s="43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E126" s="43" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="F126" s="43" t="s">
         <v>156</v>
@@ -25433,10 +25433,10 @@
         <v>156</v>
       </c>
       <c r="P398" s="43" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q398" s="44" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R398" s="44" t="s">
         <v>156</v>
@@ -41260,38 +41260,38 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C2" t="s">
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C3" t="s">
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C4" t="s">
         <v>32</v>
@@ -41302,7 +41302,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -41311,26 +41311,26 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -41344,21 +41344,21 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B8" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C8" t="s">
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -41367,40 +41367,40 @@
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
@@ -41409,12 +41409,12 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
@@ -41423,26 +41423,26 @@
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B14" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C14" t="s">
         <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B15" t="s">
         <v>25</v>
@@ -41456,38 +41456,38 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B16" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B17" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C17" t="s">
         <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B18" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C18" t="s">
         <v>32</v>
@@ -41498,21 +41498,21 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C19" t="s">
         <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B20" t="s">
         <v>118</v>
@@ -41526,10 +41526,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B21" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C21" t="s">
         <v>32</v>
@@ -41540,30 +41540,30 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B22" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C22" t="s">
         <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B23" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C23" t="s">
         <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -41571,18 +41571,18 @@
         <v>136</v>
       </c>
       <c r="B24" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C24" t="s">
         <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B25" t="s">
         <v>106</v>
@@ -41596,21 +41596,21 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B26" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C26" t="s">
         <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B27" t="s">
         <v>119</v>
@@ -41619,29 +41619,29 @@
         <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B28" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B29" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -41652,24 +41652,24 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B30" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B31" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C31" t="s">
         <v>32</v>
@@ -41680,7 +41680,7 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B32" t="s">
         <v>126</v>
@@ -41689,29 +41689,29 @@
         <v>32</v>
       </c>
       <c r="D32" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B33" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C33" t="s">
         <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C34" t="s">
         <v>32</v>
@@ -41722,7 +41722,7 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B35" t="s">
         <v>21</v>
@@ -41736,35 +41736,35 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B36" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C36" t="s">
         <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B37" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C37" t="s">
         <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B38" t="s">
         <v>138</v>
@@ -41773,12 +41773,12 @@
         <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B39" t="s">
         <v>23</v>
@@ -41787,15 +41787,15 @@
         <v>32</v>
       </c>
       <c r="D39" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B40" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C40" t="s">
         <v>32</v>
@@ -41806,7 +41806,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B41" t="s">
         <v>31</v>
@@ -41815,12 +41815,12 @@
         <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B42" t="s">
         <v>95</v>
@@ -41829,12 +41829,12 @@
         <v>32</v>
       </c>
       <c r="D42" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B43" t="s">
         <v>117</v>
@@ -41843,12 +41843,12 @@
         <v>32</v>
       </c>
       <c r="D43" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B44" t="s">
         <v>96</v>
@@ -41857,12 +41857,12 @@
         <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B45" t="s">
         <v>199</v>
@@ -41876,7 +41876,7 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B46" t="s">
         <v>140</v>
@@ -41885,12 +41885,12 @@
         <v>32</v>
       </c>
       <c r="D46" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B47" t="s">
         <v>28</v>
@@ -41899,40 +41899,40 @@
         <v>32</v>
       </c>
       <c r="D47" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B48" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B49" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
       </c>
       <c r="D49" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B50" t="s">
         <v>139</v>
@@ -41946,24 +41946,24 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B51" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C51" t="s">
         <v>32</v>
       </c>
       <c r="D51" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B52" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C52" t="s">
         <v>32</v>
@@ -41974,49 +41974,49 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B53" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C53" t="s">
         <v>32</v>
       </c>
       <c r="D53" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B54" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C54" t="s">
         <v>32</v>
       </c>
       <c r="D54" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B55" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
       </c>
       <c r="D55" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B56" t="s">
         <v>137</v>
@@ -42030,7 +42030,7 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B57" t="s">
         <v>22</v>
@@ -42039,54 +42039,54 @@
         <v>32</v>
       </c>
       <c r="D57" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B58" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
       </c>
       <c r="D58" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B59" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
       </c>
       <c r="D59" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B60" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
       </c>
       <c r="D60" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B61" t="s">
         <v>24</v>
@@ -42100,21 +42100,21 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B62" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
       </c>
       <c r="D62" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B63" t="s">
         <v>142</v>
@@ -42123,29 +42123,29 @@
         <v>32</v>
       </c>
       <c r="D63" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B64" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C64" t="s">
         <v>32</v>
       </c>
       <c r="D64" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B65" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C65" t="s">
         <v>32</v>
@@ -42156,24 +42156,24 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B66" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C66" t="s">
         <v>32</v>
       </c>
       <c r="D66" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B67" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C67" t="s">
         <v>32</v>
@@ -42184,24 +42184,24 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B68" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C68" t="s">
         <v>32</v>
       </c>
       <c r="D68" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B69" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C69" t="s">
         <v>32</v>
@@ -42212,63 +42212,63 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B70" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C70" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D70" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B71" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C71" t="s">
         <v>32</v>
       </c>
       <c r="D71" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B72" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C72" t="s">
         <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B73" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C73" t="s">
         <v>32</v>
       </c>
       <c r="D73" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B74" t="s">
         <v>96</v>
@@ -42282,35 +42282,35 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B75" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C75" t="s">
         <v>32</v>
       </c>
       <c r="D75" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B76" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C76" t="s">
         <v>32</v>
       </c>
       <c r="D76" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B77" t="s">
         <v>19</v>
@@ -42319,26 +42319,26 @@
         <v>32</v>
       </c>
       <c r="D77" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B78" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C78" t="s">
         <v>32</v>
       </c>
       <c r="D78" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B79" t="s">
         <v>30</v>
@@ -42347,21 +42347,21 @@
         <v>32</v>
       </c>
       <c r="D79" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B80" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C80" t="s">
         <v>32</v>
       </c>
       <c r="D80" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
   </sheetData>
@@ -42416,16 +42416,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C2" t="s">
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
   </sheetData>
